--- a/docs/test-cases/SPM-24_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-24_Test_Cases.xlsx
@@ -25,6 +25,7 @@
     <sheet name="TC15" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="TC16" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="TC17" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TC18" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -464,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -920,7 +921,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Replacing equipment with the same item twice in a draft edit is rejected</t>
+          <t>An equipment item already chosen in one row is not offered again in another row</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -930,7 +931,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -947,27 +948,27 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>SPM-24-TC14</t>
+          <t>SPM-24-TC13b</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>A complete draft can be submitted and leaves draft status</t>
+          <t>"Add equipment" is disabled once every catalogue item is already in the request</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>AC1, AC5</t>
+          <t>AC4</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Acceptance Criteria</t>
+          <t>Code</t>
         </is>
       </c>
     </row>
@@ -979,27 +980,27 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>SPM-24-TC15</t>
+          <t>SPM-24-TC14</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>An incomplete draft cannot be submitted from its edit page</t>
+          <t>A complete draft can be submitted and leaves draft status</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>AC5</t>
+          <t>AC1, AC5</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Acceptance Criteria</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1012,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>SPM-24-TC16</t>
+          <t>SPM-24-TC15</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>A draft never appears in the Submitted section of the owner's own events page</t>
+          <t>An incomplete draft cannot be submitted from its edit page</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1026,7 +1027,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -1043,64 +1044,96 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
+          <t>SPM-24-TC16</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>A draft never appears in the Submitted section of the owner's own events page</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>AC5</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>TC18</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
           <t>SPM-24-TC17</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>A non-organiser role never sees another user's draft in the events list</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>AC3, AC5</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Covered by</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>AC1</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Given I have entered some event information, when I select "Save Draft", then the request is saved.</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="9" t="n"/>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Covered by</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>AC1</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Given I have entered some event information, when I select "Save Draft", then the request is saved.</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>SPM-24-TC01
 SPM-24-TC02
@@ -1108,43 +1141,43 @@
 SPM-24-TC14</t>
         </is>
       </c>
-      <c r="F24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="31" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="F25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="31" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>A saved draft is clearly identified as a draft.</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC04
-SPM-24-TC05</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="n"/>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>AC3</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>I can leave the system and return to the draft later.</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>SPM-24-TC04
+SPM-24-TC05</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>AC3</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>I can leave the system and return to the draft later.</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>SPM-24-TC06
 SPM-24-TC07
@@ -1152,46 +1185,47 @@
 SPM-24-TC17</t>
         </is>
       </c>
-      <c r="F26" s="9" t="n"/>
-    </row>
-    <row r="27" ht="71.5" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="F27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="85" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>I can edit the information in the draft.</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>SPM-24-TC09
 SPM-24-TC10
 SPM-24-TC11
 SPM-24-TC12
-SPM-24-TC13</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="n"/>
-    </row>
-    <row r="28" ht="71.5" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+SPM-24-TC13
+SPM-24-TC13b</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="71.5" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>A draft is not treated as a submitted event request.</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>SPM-24-TC12
 SPM-24-TC14
@@ -1200,15 +1234,15 @@
 SPM-24-TC17</t>
         </is>
       </c>
-      <c r="F28" s="9" t="n"/>
-    </row>
-    <row r="30" ht="152.5" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="F29" s="9" t="n"/>
+    </row>
+    <row r="31" ht="152.5" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>src/lib/validation.ts
 src/lib/eventForm.ts
@@ -1223,24 +1257,24 @@
 prisma/seed.ts</t>
         </is>
       </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="9" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B30:F30"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E29:F29"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B31:F31"/>
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B24:D24"/>
@@ -1263,6 +1297,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2100,7 +2135,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="17.5" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2108,11 +2143,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The draft from TC09 already has Starts at and Ends at saved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="85" customHeight="1">
+          <t>The draft from TC09 already has Starts at and Ends at saved. The equipment catalogue has at least two active items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2121,13 +2156,13 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Open the draft's "Edit draft" page
-2. Add an equipment row, choose "4K Portable Projector", quantity 1
-3. Add a second equipment row, choose "4K Portable Projector" again, quantity 2
-4. Click "Save draft"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
+2. Click "Add equipment" and choose "4K Portable Projector" in the first row
+3. Click "Add equipment" again to add a second row
+4. Open the second row's equipment dropdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2135,7 +2170,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Equipment: "4K Portable Projector" chosen in two separate rows</t>
+          <t>First row: 4K Portable Projector</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2182,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The page does not move on. A message "Each item can only be requested once — change the quantity instead of adding a second row." appears above the equipment rows, and the draft's saved equipment is unchanged.</t>
+          <t>"4K Portable Projector" is not listed as an option in the second row's dropdown — only items not already chosen elsewhere are offered. Choosing a different item in the second row and clicking "Save draft" saves both rows successfully.</t>
         </is>
       </c>
     </row>
@@ -2256,11 +2291,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-24-TC14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
+          <t>SPM-24-TC13b</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2268,11 +2303,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The draft from TC09 has Event name, Type, Starts at and Ends at set. Expected attendance is still missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+          <t>The draft from TC09 already has Starts at and Ends at saved. Note the total number of active items shown across the equipment dropdown (N).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2281,12 +2316,11 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Open the draft's "Edit draft" page
-2. Enter 120 into Expected attendance
-3. Click "Submit request"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
+2. Click "Add equipment" and pick a different, not-yet-chosen item in each row, N times in total, until every catalogue item has been used</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2294,7 +2328,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Expected attendance: 120 (everything else already saved from TC09)</t>
+          <t>One row per catalogue item, no repeats</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2340,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The browser moves to the event's own page. Its status badge now reads "Submitted" instead of "Draft", and it no longer appears under "Drafts — not yet submitted" on "My events".</t>
+          <t>Once the last item is chosen, the "Add equipment" button becomes disabled and the text "Every catalogue item is already in your request." appears beneath it.</t>
         </is>
       </c>
     </row>
@@ -2415,11 +2449,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-24-TC15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="58" customHeight="1">
+          <t>SPM-24-TC14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2427,7 +2461,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The seeded draft "Q1 Investor Update (rough idea)", owned by rachel.ng@meridianfina.com, has only a title and description — Type of event, Starts at, Ends at and Expected attendance are all still empty.</t>
+          <t>The draft from TC09 has Event name, Type, Starts at and Ends at set. Expected attendance is still missing.</t>
         </is>
       </c>
     </row>
@@ -2439,13 +2473,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Log in as rachel.ng@meridianfina.com / password123
-2. Open the draft's "Edit draft" page
-3. Without filling anything else in, click "Submit request"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.5" customHeight="1">
+          <t>1. Open the draft's "Edit draft" page
+2. Enter 120 into Expected attendance
+3. Click "Submit request"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2453,11 +2487,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>N/A — submitting the draft exactly as saved</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+          <t>Expected attendance: 120 (everything else already saved from TC09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2465,7 +2499,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The page does not move on. Messages appear at once under Type of event, Starts at, Ends at and Expected attendance, listing what's still needed; the draft is left exactly as it was, still showing the "Draft" badge.</t>
+          <t>The browser moves to the event's own page. Its status badge now reads "Submitted" instead of "Draft", and it no longer appears under "Drafts — not yet submitted" on "My events".</t>
         </is>
       </c>
     </row>
@@ -2574,11 +2608,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-24-TC16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.5" customHeight="1">
+          <t>SPM-24-TC15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2586,11 +2620,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Seeded account rachel.ng@meridianfina.com owns the seeded draft "Q1 Investor Update (rough idea)" and the seeded, already-completed event "Meridian Compliance Training".</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="31" customHeight="1">
+          <t>The seeded draft "Q1 Investor Update (rough idea)", owned by rachel.ng@meridianfina.com, has only a title and description — Type of event, Starts at, Ends at and Expected attendance are all still empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2599,7 +2633,8 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Log in as rachel.ng@meridianfina.com / password123
-2. Open the "My events" page</t>
+2. Open the draft's "Edit draft" page
+3. Without filling anything else in, click "Submit request"</t>
         </is>
       </c>
     </row>
@@ -2611,11 +2646,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>N/A — uses seeded data</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+          <t>N/A — submitting the draft exactly as saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2623,7 +2658,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The draft appears only under "Drafts — not yet submitted". The "Submitted" section lists "Meridian Compliance Training" but not "Q1 Investor Update (rough idea)".</t>
+          <t>The page does not move on. Messages appear at once under Type of event, Starts at, Ends at and Expected attendance, listing what's still needed; the draft is left exactly as it was, still showing the "Draft" badge.</t>
         </is>
       </c>
     </row>
@@ -2732,11 +2767,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-24-TC17</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.5" customHeight="1">
+          <t>SPM-24-TC16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2744,7 +2779,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>daniel.tan@connectsphere.com is a seeded Coordinator who owns no events of his own. rachel.ng@meridianfina.com owns the seeded draft "Q1 Investor Update (rough idea)". budi.santoso@nusantaratec.com owns the seeded, already-submitted event "Nusantara Developer Summit".</t>
+          <t>Seeded account rachel.ng@meridianfina.com owns the seeded draft "Q1 Investor Update (rough idea)" and the seeded, already-completed event "Meridian Compliance Training".</t>
         </is>
       </c>
     </row>
@@ -2756,8 +2791,8 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Log in as daniel.tan@connectsphere.com / password123
-2. Open the "All events" page</t>
+          <t>1. Log in as rachel.ng@meridianfina.com / password123
+2. Open the "My events" page</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2816,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>"Nusantara Developer Summit" appears in the list. "Q1 Investor Update (rough idea)", or any other draft, does not appear anywhere on the page.</t>
+          <t>The draft appears only under "Drafts — not yet submitted". The "Submitted" section lists "Meridian Compliance Training" but not "Q1 Investor Update (rough idea)".</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2927,177 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="17.5" customHeight="1">
+    <row r="2" ht="152.5" customHeight="1">
       <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>None raised</t>
+          <t>SPM-24-TC13 originally tested that selecting the same equipment item twice was rejected after the fact, with an error message. The picker was changed so a duplicate can no longer be selected in the first place (the already-chosen item is removed from the other rows' dropdowns), which is why TC13 now tests prevention instead of rejection, and TC13b was added for the 'every item already used' edge case. The server-side Zod rule that used to produce the rejection message is still in place as a safety net (src/lib/validation/events.ts) but is no longer reachable by clicking through the app, so it isn't covered by a manual test case here — only by the existing unit test in src/lib/__tests__/validation.test.ts.</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-24-TC17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.5" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>daniel.tan@connectsphere.com is a seeded Coordinator who owns no events of his own. rachel.ng@meridianfina.com owns the seeded draft "Q1 Investor Update (rough idea)". budi.santoso@nusantaratec.com owns the seeded, already-submitted event "Nusantara Developer Summit".</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="31" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Open the "All events" page</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>N/A — uses seeded data</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>"Nusantara Developer Summit" appears in the list. "Q1 Investor Update (rough idea)", or any other draft, does not appear anywhere on the page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/docs/test-cases/SPM-24_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-24_Test_Cases.xlsx
@@ -4,23 +4,24 @@
   <workbookPr/>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TC01" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TC02" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TC03" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TC04" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TC05" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TC06" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TC07" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TC08" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TC09" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="TC10" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="TC11" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="TC12" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="TC13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="TC14" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="TC15" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="TC16" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="TC17" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Open Questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TC02" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TC03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TC04" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TC05" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TC06" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TC07" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TC08" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TC09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TC10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="TC11" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="TC12" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="TC13" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="TC14" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="TC15" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TC16" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="TC17" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -170,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -252,6 +253,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -543,12 +550,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="31">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="34" t="inlineStr">
         <is>
           <t>SPM-24: As an Event Organiser, I want to save an incomplete event request as a draft so that I can complete or review it before submitting it.</t>
         </is>
@@ -560,32 +567,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="34" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="34" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -612,27 +619,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC01</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>Save Draft creates a saved draft with only a title</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -651,27 +658,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC02</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Save Draft is blocked when the event name is empty</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -690,27 +697,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC03</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Save Draft treats a whitespace-only title the same as empty</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -729,27 +736,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC04</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>A saved draft is shown under its own 'Drafts' section with a Draft badge</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -768,27 +775,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC05</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Opening a draft also shows the Draft badge on its own page</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -807,27 +814,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC06</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Organiser can leave and return to a saved draft</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="35" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -846,27 +853,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC07</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>A draft is not visible to an unrelated organiser</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -885,27 +892,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC08</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>Visiting a draft's edit link while logged out redirects to login</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -924,27 +931,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC09</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>Editing a draft's fields saves the changes</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="35" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -963,27 +970,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC10</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>Changing only the end time is checked against the already-saved start time</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1002,27 +1009,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC11</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>Changing the end time to before the already-saved start time is rejected</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1041,27 +1048,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC12</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>A draft that gets submitted in another tab can no longer be saved from a stale edit tab</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>AC4, AC5</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1080,27 +1087,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC13</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>Replacing equipment with the same item twice in a draft edit is rejected</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1119,27 +1126,27 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC14</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>A complete draft can be submitted and leaves draft status</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
         <is>
           <t>AC1, AC5</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="35" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1158,27 +1165,27 @@
           <t>TC15</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC15</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>An incomplete draft cannot be submitted from its edit page</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="35" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="35" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1197,27 +1204,27 @@
           <t>TC16</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC16</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>A draft never appears in the Submitted section of the owner's own events page</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1236,27 +1243,27 @@
           <t>TC17</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC17</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>A non-organiser role never sees another user's draft in the events list</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>AC3, AC5</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1272,19 +1279,19 @@
     <row r="21" ht="15.75" customHeight="1" s="31"/>
     <row r="22" ht="15.75" customHeight="1" s="31"/>
     <row r="23" ht="15.75" customHeight="1" s="31">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C23" s="32" t="n"/>
       <c r="D23" s="33" t="n"/>
-      <c r="E23" s="1" t="inlineStr">
+      <c r="E23" s="34" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1292,19 +1299,19 @@
       <c r="F23" s="33" t="n"/>
     </row>
     <row r="24" ht="57.75" customHeight="1" s="31">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Given I have entered some event information, when I select "Save Draft", then the request is saved.</t>
         </is>
       </c>
       <c r="C24" s="32" t="n"/>
       <c r="D24" s="33" t="n"/>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC01
 SPM-24-TC02
@@ -1315,19 +1322,19 @@
       <c r="F24" s="33" t="n"/>
     </row>
     <row r="25" ht="30.75" customHeight="1" s="31">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>A saved draft is clearly identified as a draft.</t>
         </is>
       </c>
       <c r="C25" s="32" t="n"/>
       <c r="D25" s="33" t="n"/>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC04
 SPM-24-TC05</t>
@@ -1336,19 +1343,19 @@
       <c r="F25" s="33" t="n"/>
     </row>
     <row r="26" ht="57.75" customHeight="1" s="31">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>I can leave the system and return to the draft later.</t>
         </is>
       </c>
       <c r="C26" s="32" t="n"/>
       <c r="D26" s="33" t="n"/>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC06
 SPM-24-TC07
@@ -1359,19 +1366,19 @@
       <c r="F26" s="33" t="n"/>
     </row>
     <row r="27" ht="71.25" customHeight="1" s="31">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>I can edit the information in the draft.</t>
         </is>
       </c>
       <c r="C27" s="32" t="n"/>
       <c r="D27" s="33" t="n"/>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC09
 SPM-24-TC10
@@ -1383,19 +1390,19 @@
       <c r="F27" s="33" t="n"/>
     </row>
     <row r="28" ht="71.25" customHeight="1" s="31">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>A draft is not treated as a submitted event request.</t>
         </is>
       </c>
       <c r="C28" s="32" t="n"/>
       <c r="D28" s="33" t="n"/>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC12
 SPM-24-TC14
@@ -1408,12 +1415,12 @@
     </row>
     <row r="29" ht="15.75" customHeight="1" s="31"/>
     <row r="30" ht="152.25" customHeight="1" s="31">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>src/lib/validation.ts
 src/lib/eventForm.ts
@@ -2472,9 +2479,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC09</t>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC08</t>
         </is>
       </c>
     </row>
@@ -2484,50 +2491,46 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Draft "Annual Partner Appreciation Dinner" from TC01, owned by rachel.ng@meridianfina.com, has no other fields set yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="111.75" customHeight="1" s="31">
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Seeded draft "Q1 Investor Update (rough idea)" exists. No one is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="31">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Log in as rachel.ng@meridianfina.com / password123
-2. Open the draft's "Edit draft" page
-3. Change Event name to "Annual Partner Appreciation Dinner - Updated"
-4. Set Type of event to "Conference"
-5. Set Starts at to 10 Nov 2026, 9:00 AM and Ends at to 10 Nov 2026, 5:00 PM
-6. Click "Save draft"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.25" customHeight="1" s="31">
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. Make sure you are logged out
+2. Paste the draft's edit-page address into the browser and go to it</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="31">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event name: Annual Partner Appreciation Dinner - Updated; Type of event: Conference; Starts at: 10 Nov 2026, 9:00 AM; Ends at: 10 Nov 2026, 5:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30.75" customHeight="1" s="31">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="31">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The browser returns to "My events". Status remains "Draft". Reopening the draft shows all the updated values.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The browser is redirected to the login page instead of showing the draft. After logging in, it takes you straight back to the draft's edit page.</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2540,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -2569,9 +2572,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The browser returns to "My events". Status remains "Draft". Reopening the draft shows all the updated values.</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The browser is redirected to the login page instead of showing the draft. After logging in, it takes you straight back to the draft's edit page.</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2608,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -2637,9 +2640,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>The browser returns to "My events". Column when shows 10 Oct 2026, 09:00–17:00. Status remains "Draft". Reopening the draft shows all the updated values.</t>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Pasting the draft's edit URL while logged out redirects to the login page displays the message "Your session expired. Log in to continue where you left off." After logging in successfully, the browser is redirected back to the draft's edit page</t>
         </is>
       </c>
     </row>
@@ -3700,9 +3703,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC10</t>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC09</t>
         </is>
       </c>
     </row>
@@ -3712,48 +3715,50 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>The draft from TC09 already has Starts at saved as 10 Nov 2026, 9:00 AM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.25" customHeight="1" s="31">
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Draft "Annual Partner Appreciation Dinner" from TC01, owned by rachel.ng@meridianfina.com, has no other fields set yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="111.75" customHeight="1" s="31">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Open the draft's "Edit draft" page (Starts at already shows 10 Nov 2026, 9:00 AM)
-2. Change Ends at to 10 Nov 2026, 6:00 PM, without touching Starts at
-3. Click "Save draft"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="31">
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. Log in as rachel.ng@meridianfina.com / password123
+2. Open the draft's "Edit draft" page
+3. Change Event name to "Annual Partner Appreciation Dinner - Updated"
+4. Set Type of event to "Conference"
+5. Set Starts at to 10 Nov 2026, 9:00 AM and Ends at to 10 Nov 2026, 5:00 PM
+6. Click "Save draft"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1" s="31">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Ends at: 10 Nov 2026, 6:00 PM (Starts at left as already loaded, 9:00 AM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="31">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Event name: Annual Partner Appreciation Dinner - Updated; Type of event: Conference; Starts at: 10 Nov 2026, 9:00 AM; Ends at: 10 Nov 2026, 5:00 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30.75" customHeight="1" s="31">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The change is saved without error, because 6:00 PM is after the already-saved 9:00 AM start.
-Reopening the draft shows Ends at as 10 Nov 2026, 6:00 PM and Starts at unchanged at 9:00 AM.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The browser returns to "My events". Status remains "Draft". Reopening the draft shows all the updated values.</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3768,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -3795,10 +3800,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The change is saved without error, because 6:00 PM is after the already-saved 9:00 AM start.
-Reopening the draft shows Ends at as 10 Nov 2026, 6:00 PM and Starts at unchanged at 9:00 AM.</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The browser returns to "My events". Status remains "Draft". Reopening the draft shows all the updated values.</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3836,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -3864,11 +3868,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>The change is saved without error, because 6:00 PM is after the already-saved 9:00 AM start.
-The browser returns to "My events". Column when shows 10 Oct 2026, 09:00–18:00.
-Reopening the draft shows Ends at as 10 Nov 2026, 6:00 PM and Starts at unchanged at 9:00 AM.</t>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>The browser returns to "My events". Column when shows 10 Oct 2026, 09:00–17:00. Status remains "Draft". Reopening the draft shows all the updated values.</t>
         </is>
       </c>
     </row>
@@ -4907,11 +4909,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="31" min="1" max="1"/>
-    <col width="70.38" customWidth="1" style="31" min="2" max="2"/>
+    <col width="56.75" customWidth="1" style="31" min="2" max="2"/>
     <col width="12.63" customWidth="1" style="31" min="3" max="6"/>
   </cols>
   <sheetData>
@@ -4929,9 +4931,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC11</t>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC10</t>
         </is>
       </c>
     </row>
@@ -4941,22 +4943,22 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>The draft from TC09/TC10 has Starts at saved as 10 Nov 2026, 9:00 AM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="57.75" customHeight="1" s="31">
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>The draft from TC09 already has Starts at saved as 10 Nov 2026, 9:00 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.25" customHeight="1" s="31">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Open the draft's "Edit draft" page
-2. Change Ends at to 10 Nov 2026, 8:00 AM, without touching Starts at
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. Open the draft's "Edit draft" page (Starts at already shows 10 Nov 2026, 9:00 AM)
+2. Change Ends at to 10 Nov 2026, 6:00 PM, without touching Starts at
 3. Click "Save draft"</t>
         </is>
       </c>
@@ -4967,21 +4969,22 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Ends at: 10 Nov 2026, 8:00 AM (before the loaded Starts at of 9:00 AM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="31">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Ends at: 10 Nov 2026, 6:00 PM (Starts at left as already loaded, 9:00 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="31">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The page does not move on. A message "Ends at must be after starts at." appears under Ends at, and the previously saved Ends at value is not overwritten.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The change is saved without error, because 6:00 PM is after the already-saved 9:00 AM start.
+Reopening the draft shows Ends at as 10 Nov 2026, 6:00 PM and Starts at unchanged at 9:00 AM.</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4994,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -5023,9 +5026,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The page does not move on. A message "Ends at must be after starts at." appears under Ends at, and the previously saved Ends at value is not overwritten.</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The change is saved without error, because 6:00 PM is after the already-saved 9:00 AM start.
+Reopening the draft shows Ends at as 10 Nov 2026, 6:00 PM and Starts at unchanged at 9:00 AM.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5063,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -5091,11 +5095,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Ends at accepted as 10 Nov 2026, 8:00 AM. 
-Validation correctly blocked the save:  "endsAt must be after startsAt" appeared and the previously saved Ends at value was not overwritten. 
-However, the error message rendered at the top of the page and the view did not scroll to it, so from the Schedule/Attendance section (where the fields being edited are) clicking Save draft gave no visible feedback that anything had happened.</t>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>The change is saved without error, because 6:00 PM is after the already-saved 9:00 AM start.
+The browser returns to "My events". Column when shows 10 Oct 2026, 09:00–18:00.
+Reopening the draft shows Ends at as 10 Nov 2026, 6:00 PM and Starts at unchanged at 9:00 AM.</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5111,7 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5117,9 +5121,9 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>The core validation logic passes as bad input was rejected and data wasn't corrupted but the test case is checking the full save-draft flow and the missing scroll-to-error means the actual UX doesn't match the expected result of a clear inline error. Also flag the raw endsAt/startsAt field names instead of formatted labels as a second defect under the same fail.</t>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5147,72 +5151,12 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" s="31"/>
     <row r="25" ht="15.75" customHeight="1" s="31"/>
-    <row r="26" ht="15.75" customHeight="1" s="31">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" s="31">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>The page does not move on. A message "Ends at must be after starts at." appears under Ends at, and the previously saved Ends at value is not overwritten.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" s="31">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" s="31">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Feedback was given to kristen and she updated it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" s="31">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" s="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="n">
-        <v>46282</v>
-      </c>
-    </row>
+    <row r="26" ht="15.75" customHeight="1" s="31"/>
+    <row r="27" ht="15.75" customHeight="1" s="31"/>
+    <row r="28" ht="15.75" customHeight="1" s="31"/>
+    <row r="29" ht="15.75" customHeight="1" s="31"/>
+    <row r="30" ht="15.75" customHeight="1" s="31"/>
+    <row r="31" ht="15.75" customHeight="1" s="31"/>
     <row r="32" ht="15.75" customHeight="1" s="31"/>
     <row r="33" ht="15.75" customHeight="1" s="31"/>
     <row r="34" ht="15.75" customHeight="1" s="31"/>
@@ -6198,7 +6142,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="31" min="1" max="1"/>
-    <col width="56.75" customWidth="1" style="31" min="2" max="2"/>
+    <col width="70.38" customWidth="1" style="31" min="2" max="2"/>
     <col width="12.63" customWidth="1" style="31" min="3" max="6"/>
   </cols>
   <sheetData>
@@ -6216,60 +6160,59 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC12</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="57.75" customHeight="1" s="31">
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30.75" customHeight="1" s="31">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>A draft owned by rachel.ng@meridianfina.com is complete enough to submit (Event name, Type, Starts at, Ends at and Expected attendance all filled in) and is currently open on its "Edit draft" page in Tab A.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="84.75" customHeight="1" s="31">
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>The draft from TC09/TC10 has Starts at saved as 10 Nov 2026, 9:00 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="57.75" customHeight="1" s="31">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. In a second browser tab (Tab B), log in as the same organiser and open the same draft
-2. In Tab B, click "Submit request" so the event's status becomes "Submitted"
-3. Switch back to Tab A, change the Description field, and click "Save draft"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" s="31">
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. Open the draft's "Edit draft" page
+2. Change Ends at to 10 Nov 2026, 8:00 AM, without touching Starts at
+3. Click "Save draft"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="31">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Description entered in Tab A: "trying to sneak an edit in"</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="31">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Ends at: 10 Nov 2026, 8:00 AM (before the loaded Starts at of 9:00 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="31">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Tab A shows an error such as "Only draft requests can be edited."
-The event's Description is not changed, and its status remains "Submitted".</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The page does not move on. A message "Ends at must be after starts at." appears under Ends at, and the previously saved Ends at value is not overwritten.</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6222,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -6311,10 +6254,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Tab A shows an error such as "Only draft requests can be edited."
-The event's Description is not changed, and its status remains "Submitted".</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The page does not move on. A message "Ends at must be after starts at." appears under Ends at, and the previously saved Ends at value is not overwritten.</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6290,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -6380,9 +6322,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Tab A blocked the save. "Only draft requests can be edited." appeared, Description was not persisted, and status remained "Submitted." Same issue as TC11 though: the error rendered at the top of the page with no scroll-to-error, so from wherever the Description field sits on the page, clicking Save draft gave no visible confirmation that the save had failed (or succeeded, or done anything).</t>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Ends at accepted as 10 Nov 2026, 8:00 AM. 
+Validation correctly blocked the save:  "endsAt must be after startsAt" appeared and the previously saved Ends at value was not overwritten. 
+However, the error message rendered at the top of the page and the view did not scroll to it, so from the Schedule/Attendance section (where the fields being edited are) clicking Save draft gave no visible feedback that anything had happened.</t>
         </is>
       </c>
     </row>
@@ -6404,9 +6348,9 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>Confirms the scroll-to-error defect from TC11 isn't isolated to the startsAt/endsAt validation, it's a general pattern on this form: any failed Save draft renders its error at the top with no scroll or focus shift, regardless of which field triggered it or where on the page the user is. Worth raising as one bug covering the whole form rather than one per test case. Recommend citing TC11 in the ticket as a duplicate symptom.</t>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>The core validation logic passes as bad input was rejected and data wasn't corrupted but the test case is checking the full save-draft flow and the missing scroll-to-error means the actual UX doesn't match the expected result of a clear inline error. Also flag the raw endsAt/startsAt field names instead of formatted labels as a second defect under the same fail.</t>
         </is>
       </c>
     </row>
@@ -6448,10 +6392,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Tab A shows an error such as "Only draft requests can be edited."
-The event's Description is not changed, and its status remains "Submitted".</t>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>The page does not move on. A message "Ends at must be after starts at." appears under Ends at, and the previously saved Ends at value is not overwritten.</t>
         </is>
       </c>
     </row>
@@ -6485,7 +6428,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -7504,21 +7447,21 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17.25" customHeight="1" s="31">
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="57.75" customHeight="1" s="31">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>The draft from TC09 already has Starts at and Ends at saved.</t>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>A draft owned by rachel.ng@meridianfina.com is complete enough to submit (Event name, Type, Starts at, Ends at and Expected attendance all filled in) and is currently open on its "Edit draft" page in Tab A.</t>
         </is>
       </c>
     </row>
@@ -7528,24 +7471,23 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
-        <is>
-          <t>1. Open the draft's "Edit draft" page
- 2. Click "Add equipment" and choose "4K Portable Projector" in the first row
- 3. Click "Add equipment" again to add a second row
- 4. Open the second row's equipment dropdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="31">
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. In a second browser tab (Tab B), log in as the same organiser and open the same draft
+2. In Tab B, click "Submit request" so the event's status becomes "Submitted"
+3. Switch back to Tab A, change the Description field, and click "Save draft"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="31">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
-        <is>
-          <t>First row: 4K Portable Projector</t>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Description entered in Tab A: "trying to sneak an edit in"</t>
         </is>
       </c>
     </row>
@@ -7555,9 +7497,10 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
-        <is>
-          <t>"4K Portable Projector" is not listed as an option in the second row's dropdown — only items not already chosen elsewhere are offered. Choosing a different item in the second row and clicking "Save draft" saves both rows successfully.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Tab A shows an error such as "Only draft requests can be edited."
+The event's Description is not changed, and its status remains "Submitted".</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7510,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7599,9 +7542,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>"4K Portable Projector" is not listed as an option in the second row's dropdown — only items not already chosen elsewhere are offered. Choosing a different item in the second row and clicking "Save draft" saves both rows successfully.</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Tab A shows an error such as "Only draft requests can be edited."
+The event's Description is not changed, and its status remains "Submitted".</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7579,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7667,9 +7611,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>Duplicate equipment row blocked. "Each piece of equipment can only be requested once — change the quantity instead" appeared above the equipment rows, save did not go through, and the draft's saved equipment was unchanged. Same scroll-to-error issue as TC11/TC12, error appears above the equipment rows but doesn't pull the view to it, so it's easy to miss if you're not looking at that part of the page already.</t>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Tab A blocked the save. "Only draft requests can be edited." appeared, Description was not persisted, and status remained "Submitted." Same issue as TC11 though: the error rendered at the top of the page with no scroll-to-error, so from wherever the Description field sits on the page, clicking Save draft gave no visible confirmation that the save had failed (or succeeded, or done anything).</t>
         </is>
       </c>
     </row>
@@ -7691,11 +7635,9 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="30" t="inlineStr">
-        <is>
-          <t>Two things to note: 
-(1) same scroll-to-error defect as TC11/TC12 strengthens the case for one form-wide ticket rather than three separate ones. 
-(2) Message text differs from the expected copy, got "Each piece of equipment can only be requested once — change the quantity instead" vs. spec's "Each item can only be requested once — change the quantity instead of adding a second row."</t>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>Confirms the scroll-to-error defect from TC11 isn't isolated to the startsAt/endsAt validation, it's a general pattern on this form: any failed Save draft renders its error at the top with no scroll or focus shift, regardless of which field triggered it or where on the page the user is. Worth raising as one bug covering the whole form rather than one per test case. Recommend citing TC11 in the ticket as a duplicate symptom.</t>
         </is>
       </c>
     </row>
@@ -7737,9 +7679,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
-        <is>
-          <t>"4K Portable Projector" is not listed as an option in the second row's dropdown — only items not already chosen elsewhere are offered. Choosing a different item in the second row and clicking "Save draft" saves both rows successfully.</t>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>Tab A shows an error such as "Only draft requests can be edited."
+The event's Description is not changed, and its status remains "Submitted".</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7716,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -8770,7 +8713,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="31" min="1" max="1"/>
@@ -8792,35 +8735,36 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30.75" customHeight="1" s="31">
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" s="31">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>The draft from TC09 has Event name, Type, Starts at and Ends at set. Expected attendance is still missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1" s="31">
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>The draft from TC09 already has Starts at and Ends at saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="84.75" customHeight="1" s="31">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open the draft's "Edit draft" page
-2. Enter 120 into Expected attendance
-3. Click "Submit request"</t>
+ 2. Click "Add equipment" and choose "4K Portable Projector" in the first row
+ 3. Click "Add equipment" again to add a second row
+ 4. Open the second row's equipment dropdown</t>
         </is>
       </c>
     </row>
@@ -8830,21 +8774,21 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Expected attendance: 120 (everything else already saved from TC09)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="31">
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>First row: 4K Portable Projector</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="31">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The browser moves to the event's own page. Its status badge now reads "Submitted" instead of "Draft", and it no longer appears under "Drafts — not yet submitted" on "My events".</t>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>"4K Portable Projector" is not listed as an option in the second row's dropdown — only items not already chosen elsewhere are offered. Choosing a different item in the second row and clicking "Save draft" saves both rows successfully.</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8798,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -8886,9 +8830,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The browser moves to the event's own page. Its status badge now reads "Submitted" instead of "Draft", and it no longer appears under "Drafts — not yet submitted" on "My events".</t>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>"4K Portable Projector" is not listed as an option in the second row's dropdown — only items not already chosen elsewhere are offered. Choosing a different item in the second row and clicking "Save draft" saves both rows successfully.</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8856,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Event's own page not developed yet hence 404 is seen first</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8866,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -8954,9 +8898,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>The browser moves to the event's own page. Its status badge now reads "Submitted" instead of "Draft", and it no longer appears under "Drafts — not yet submitted" on "My events".</t>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Duplicate equipment row blocked. "Each piece of equipment can only be requested once — change the quantity instead" appeared above the equipment rows, save did not go through, and the draft's saved equipment was unchanged. Same scroll-to-error issue as TC11/TC12, error appears above the equipment rows but doesn't pull the view to it, so it's easy to miss if you're not looking at that part of the page already.</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8912,7 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -8978,9 +8922,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Event's own page not developed yet hence 404 is seen first</t>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Two things to note: 
+(1) same scroll-to-error defect as TC11/TC12 strengthens the case for one form-wide ticket rather than three separate ones. 
+(2) Message text differs from the expected copy, got "Each piece of equipment can only be requested once — change the quantity instead" vs. spec's "Each item can only be requested once — change the quantity instead of adding a second row."</t>
         </is>
       </c>
     </row>
@@ -8990,9 +8936,9 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Janelle</t>
         </is>
       </c>
     </row>
@@ -9002,18 +8948,78 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
-        <v>46281</v>
+      <c r="B23" s="23" t="n">
+        <v>46282</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="31"/>
     <row r="25" ht="15.75" customHeight="1" s="31"/>
-    <row r="26" ht="15.75" customHeight="1" s="31"/>
-    <row r="27" ht="15.75" customHeight="1" s="31"/>
-    <row r="28" ht="15.75" customHeight="1" s="31"/>
-    <row r="29" ht="15.75" customHeight="1" s="31"/>
-    <row r="30" ht="15.75" customHeight="1" s="31"/>
-    <row r="31" ht="15.75" customHeight="1" s="31"/>
+    <row r="26" ht="15.75" customHeight="1" s="31">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="31">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>"4K Portable Projector" is not listed as an option in the second row's dropdown — only items not already chosen elsewhere are offered. Choosing a different item in the second row and clicking "Save draft" saves both rows successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="31">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="31">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Feedback was given to kristen and she updated it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="31">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>46282</v>
+      </c>
+    </row>
     <row r="32" ht="15.75" customHeight="1" s="31"/>
     <row r="33" ht="15.75" customHeight="1" s="31"/>
     <row r="34" ht="15.75" customHeight="1" s="31"/>
@@ -10017,21 +10023,21 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="57.75" customHeight="1" s="31">
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30.75" customHeight="1" s="31">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>The seeded draft "Q1 Investor Update (rough idea)", owned by rachel.ng@meridianfina.com, has only a title and description — Type of event, Starts at, Ends at and Expected attendance are all still empty.</t>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>The draft from TC09 has Event name, Type, Starts at and Ends at set. Expected attendance is still missing.</t>
         </is>
       </c>
     </row>
@@ -10041,35 +10047,35 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Log in as rachel.ng@meridianfina.com / password123
-2. Open the draft's "Edit draft" page
-3. Without filling anything else in, click "Submit request"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" s="31">
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. Open the draft's "Edit draft" page
+2. Enter 120 into Expected attendance
+3. Click "Submit request"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="31">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>N/A — submitting the draft exactly as saved</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="31">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Expected attendance: 120 (everything else already saved from TC09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="31">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The page does not move on. Messages appear at once under Type of event, Starts at, Ends at and Expected attendance, listing what's still needed; the draft is left exactly as it was, still showing the "Draft" badge.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The browser moves to the event's own page. Its status badge now reads "Submitted" instead of "Draft", and it no longer appears under "Drafts — not yet submitted" on "My events".</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10085,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -10111,9 +10117,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The page does not move on. Messages appear at once under Type of event, Starts at, Ends at and Expected attendance, listing what's still needed; the draft is left exactly as it was, still showing the "Draft" badge.</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The browser moves to the event's own page. Its status badge now reads "Submitted" instead of "Draft", and it no longer appears under "Drafts — not yet submitted" on "My events".</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10143,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Event's own page not developed yet hence 404 is seen first</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10153,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -10179,9 +10185,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
-        <is>
-          <t>Submit blocked, draft remains "Draft." All four required fields show inline errors at once: "Choose the type of event." under Type of event, "Enter when the event starts." under Starts at, "Enter when the event ends." under Ends at, and "Enter how many people you expect." under Expected attendance. This matches the expected result once you scroll to see the full form.</t>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>The browser moves to the event's own page. Its status badge now reads "Submitted" instead of "Draft", and it no longer appears under "Drafts — not yet submitted" on "My events".</t>
         </is>
       </c>
     </row>
@@ -10203,9 +10209,9 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Event's own page not developed yet hence 404 is seen first</t>
         </is>
       </c>
     </row>
@@ -10215,9 +10221,9 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>Janelle</t>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>Kristen</t>
         </is>
       </c>
     </row>
@@ -10227,8 +10233,8 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="23" t="n">
-        <v>46282</v>
+      <c r="B23" s="26" t="n">
+        <v>46281</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="31"/>
@@ -11242,34 +11248,35 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.25" customHeight="1" s="31">
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="57.75" customHeight="1" s="31">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Seeded account rachel.ng@meridianfina.com owns the seeded draft "Q1 Investor Update (rough idea)" and the seeded, already-completed event "Meridian Compliance Training".</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30.75" customHeight="1" s="31">
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>The seeded draft "Q1 Investor Update (rough idea)", owned by rachel.ng@meridianfina.com, has only a title and description — Type of event, Starts at, Ends at and Expected attendance are all still empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="31">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>1. Log in as rachel.ng@meridianfina.com / password123
-2. Open the "My events" page</t>
+2. Open the draft's "Edit draft" page
+3. Without filling anything else in, click "Submit request"</t>
         </is>
       </c>
     </row>
@@ -11279,21 +11286,21 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>N/A — uses seeded data</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="31">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>N/A — submitting the draft exactly as saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="31">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The draft appears only under "Drafts — not yet submitted". The "Submitted" section lists "Meridian Compliance Training" but not "Q1 Investor Update (rough idea)".</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The page does not move on. Messages appear at once under Type of event, Starts at, Ends at and Expected attendance, listing what's still needed; the draft is left exactly as it was, still showing the "Draft" badge.</t>
         </is>
       </c>
     </row>
@@ -11303,7 +11310,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -11335,9 +11342,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The draft appears only under "Drafts — not yet submitted". The "Submitted" section lists "Meridian Compliance Training" but not "Q1 Investor Update (rough idea)".</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The page does not move on. Messages appear at once under Type of event, Starts at, Ends at and Expected attendance, listing what's still needed; the draft is left exactly as it was, still showing the "Draft" badge.</t>
         </is>
       </c>
     </row>
@@ -11371,7 +11378,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -11403,9 +11410,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>The draft appears only under "Drafts — not yet submitted". The "Submitted" section lists "Meridian Compliance Training" but not "Q1 Investor Update (rough idea)".</t>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Submit blocked, draft remains "Draft." All four required fields show inline errors at once: "Choose the type of event." under Type of event, "Enter when the event starts." under Starts at, "Enter when the event ends." under Ends at, and "Enter how many people you expect." under Expected attendance. This matches the expected result once you scroll to see the full form.</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11434,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -12466,21 +12473,21 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC17</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.25" customHeight="1" s="31">
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.25" customHeight="1" s="31">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>daniel.tan@connectsphere.com is a seeded Coordinator who owns no events of his own. rachel.ng@meridianfina.com owns the seeded draft "Q1 Investor Update (rough idea)". budi.santoso@nusantaratec.com owns the seeded, already-submitted event "Nusantara Developer Summit".</t>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Seeded account rachel.ng@meridianfina.com owns the seeded draft "Q1 Investor Update (rough idea)" and the seeded, already-completed event "Meridian Compliance Training".</t>
         </is>
       </c>
     </row>
@@ -12490,10 +12497,10 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Log in as daniel.tan@connectsphere.com / password123
-2. Open the "All events" page</t>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. Log in as rachel.ng@meridianfina.com / password123
+2. Open the "My events" page</t>
         </is>
       </c>
     </row>
@@ -12503,7 +12510,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>N/A — uses seeded data</t>
         </is>
@@ -12515,9 +12522,9 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>"Nusantara Developer Summit" appears in the list. "Q1 Investor Update (rough idea)", or any other draft, does not appear anywhere on the page.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The draft appears only under "Drafts — not yet submitted". The "Submitted" section lists "Meridian Compliance Training" but not "Q1 Investor Update (rough idea)".</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12534,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -12559,9 +12566,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>"Nusantara Developer Summit" appears in the list. "Q1 Investor Update (rough idea)", or any other draft, does not appear anywhere on the page.</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The draft appears only under "Drafts — not yet submitted". The "Submitted" section lists "Meridian Compliance Training" but not "Q1 Investor Update (rough idea)".</t>
         </is>
       </c>
     </row>
@@ -12595,7 +12602,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -12627,7 +12634,1231 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>The draft appears only under "Drafts — not yet submitted". The "Submitted" section lists "Meridian Compliance Training" but not "Q1 Investor Update (rough idea)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="31">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="31">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="31">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="31">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="31"/>
+    <row r="25" ht="15.75" customHeight="1" s="31"/>
+    <row r="26" ht="15.75" customHeight="1" s="31"/>
+    <row r="27" ht="15.75" customHeight="1" s="31"/>
+    <row r="28" ht="15.75" customHeight="1" s="31"/>
+    <row r="29" ht="15.75" customHeight="1" s="31"/>
+    <row r="30" ht="15.75" customHeight="1" s="31"/>
+    <row r="31" ht="15.75" customHeight="1" s="31"/>
+    <row r="32" ht="15.75" customHeight="1" s="31"/>
+    <row r="33" ht="15.75" customHeight="1" s="31"/>
+    <row r="34" ht="15.75" customHeight="1" s="31"/>
+    <row r="35" ht="15.75" customHeight="1" s="31"/>
+    <row r="36" ht="15.75" customHeight="1" s="31"/>
+    <row r="37" ht="15.75" customHeight="1" s="31"/>
+    <row r="38" ht="15.75" customHeight="1" s="31"/>
+    <row r="39" ht="15.75" customHeight="1" s="31"/>
+    <row r="40" ht="15.75" customHeight="1" s="31"/>
+    <row r="41" ht="15.75" customHeight="1" s="31"/>
+    <row r="42" ht="15.75" customHeight="1" s="31"/>
+    <row r="43" ht="15.75" customHeight="1" s="31"/>
+    <row r="44" ht="15.75" customHeight="1" s="31"/>
+    <row r="45" ht="15.75" customHeight="1" s="31"/>
+    <row r="46" ht="15.75" customHeight="1" s="31"/>
+    <row r="47" ht="15.75" customHeight="1" s="31"/>
+    <row r="48" ht="15.75" customHeight="1" s="31"/>
+    <row r="49" ht="15.75" customHeight="1" s="31"/>
+    <row r="50" ht="15.75" customHeight="1" s="31"/>
+    <row r="51" ht="15.75" customHeight="1" s="31"/>
+    <row r="52" ht="15.75" customHeight="1" s="31"/>
+    <row r="53" ht="15.75" customHeight="1" s="31"/>
+    <row r="54" ht="15.75" customHeight="1" s="31"/>
+    <row r="55" ht="15.75" customHeight="1" s="31"/>
+    <row r="56" ht="15.75" customHeight="1" s="31"/>
+    <row r="57" ht="15.75" customHeight="1" s="31"/>
+    <row r="58" ht="15.75" customHeight="1" s="31"/>
+    <row r="59" ht="15.75" customHeight="1" s="31"/>
+    <row r="60" ht="15.75" customHeight="1" s="31"/>
+    <row r="61" ht="15.75" customHeight="1" s="31"/>
+    <row r="62" ht="15.75" customHeight="1" s="31"/>
+    <row r="63" ht="15.75" customHeight="1" s="31"/>
+    <row r="64" ht="15.75" customHeight="1" s="31"/>
+    <row r="65" ht="15.75" customHeight="1" s="31"/>
+    <row r="66" ht="15.75" customHeight="1" s="31"/>
+    <row r="67" ht="15.75" customHeight="1" s="31"/>
+    <row r="68" ht="15.75" customHeight="1" s="31"/>
+    <row r="69" ht="15.75" customHeight="1" s="31"/>
+    <row r="70" ht="15.75" customHeight="1" s="31"/>
+    <row r="71" ht="15.75" customHeight="1" s="31"/>
+    <row r="72" ht="15.75" customHeight="1" s="31"/>
+    <row r="73" ht="15.75" customHeight="1" s="31"/>
+    <row r="74" ht="15.75" customHeight="1" s="31"/>
+    <row r="75" ht="15.75" customHeight="1" s="31"/>
+    <row r="76" ht="15.75" customHeight="1" s="31"/>
+    <row r="77" ht="15.75" customHeight="1" s="31"/>
+    <row r="78" ht="15.75" customHeight="1" s="31"/>
+    <row r="79" ht="15.75" customHeight="1" s="31"/>
+    <row r="80" ht="15.75" customHeight="1" s="31"/>
+    <row r="81" ht="15.75" customHeight="1" s="31"/>
+    <row r="82" ht="15.75" customHeight="1" s="31"/>
+    <row r="83" ht="15.75" customHeight="1" s="31"/>
+    <row r="84" ht="15.75" customHeight="1" s="31"/>
+    <row r="85" ht="15.75" customHeight="1" s="31"/>
+    <row r="86" ht="15.75" customHeight="1" s="31"/>
+    <row r="87" ht="15.75" customHeight="1" s="31"/>
+    <row r="88" ht="15.75" customHeight="1" s="31"/>
+    <row r="89" ht="15.75" customHeight="1" s="31"/>
+    <row r="90" ht="15.75" customHeight="1" s="31"/>
+    <row r="91" ht="15.75" customHeight="1" s="31"/>
+    <row r="92" ht="15.75" customHeight="1" s="31"/>
+    <row r="93" ht="15.75" customHeight="1" s="31"/>
+    <row r="94" ht="15.75" customHeight="1" s="31"/>
+    <row r="95" ht="15.75" customHeight="1" s="31"/>
+    <row r="96" ht="15.75" customHeight="1" s="31"/>
+    <row r="97" ht="15.75" customHeight="1" s="31"/>
+    <row r="98" ht="15.75" customHeight="1" s="31"/>
+    <row r="99" ht="15.75" customHeight="1" s="31"/>
+    <row r="100" ht="15.75" customHeight="1" s="31"/>
+    <row r="101" ht="15.75" customHeight="1" s="31"/>
+    <row r="102" ht="15.75" customHeight="1" s="31"/>
+    <row r="103" ht="15.75" customHeight="1" s="31"/>
+    <row r="104" ht="15.75" customHeight="1" s="31"/>
+    <row r="105" ht="15.75" customHeight="1" s="31"/>
+    <row r="106" ht="15.75" customHeight="1" s="31"/>
+    <row r="107" ht="15.75" customHeight="1" s="31"/>
+    <row r="108" ht="15.75" customHeight="1" s="31"/>
+    <row r="109" ht="15.75" customHeight="1" s="31"/>
+    <row r="110" ht="15.75" customHeight="1" s="31"/>
+    <row r="111" ht="15.75" customHeight="1" s="31"/>
+    <row r="112" ht="15.75" customHeight="1" s="31"/>
+    <row r="113" ht="15.75" customHeight="1" s="31"/>
+    <row r="114" ht="15.75" customHeight="1" s="31"/>
+    <row r="115" ht="15.75" customHeight="1" s="31"/>
+    <row r="116" ht="15.75" customHeight="1" s="31"/>
+    <row r="117" ht="15.75" customHeight="1" s="31"/>
+    <row r="118" ht="15.75" customHeight="1" s="31"/>
+    <row r="119" ht="15.75" customHeight="1" s="31"/>
+    <row r="120" ht="15.75" customHeight="1" s="31"/>
+    <row r="121" ht="15.75" customHeight="1" s="31"/>
+    <row r="122" ht="15.75" customHeight="1" s="31"/>
+    <row r="123" ht="15.75" customHeight="1" s="31"/>
+    <row r="124" ht="15.75" customHeight="1" s="31"/>
+    <row r="125" ht="15.75" customHeight="1" s="31"/>
+    <row r="126" ht="15.75" customHeight="1" s="31"/>
+    <row r="127" ht="15.75" customHeight="1" s="31"/>
+    <row r="128" ht="15.75" customHeight="1" s="31"/>
+    <row r="129" ht="15.75" customHeight="1" s="31"/>
+    <row r="130" ht="15.75" customHeight="1" s="31"/>
+    <row r="131" ht="15.75" customHeight="1" s="31"/>
+    <row r="132" ht="15.75" customHeight="1" s="31"/>
+    <row r="133" ht="15.75" customHeight="1" s="31"/>
+    <row r="134" ht="15.75" customHeight="1" s="31"/>
+    <row r="135" ht="15.75" customHeight="1" s="31"/>
+    <row r="136" ht="15.75" customHeight="1" s="31"/>
+    <row r="137" ht="15.75" customHeight="1" s="31"/>
+    <row r="138" ht="15.75" customHeight="1" s="31"/>
+    <row r="139" ht="15.75" customHeight="1" s="31"/>
+    <row r="140" ht="15.75" customHeight="1" s="31"/>
+    <row r="141" ht="15.75" customHeight="1" s="31"/>
+    <row r="142" ht="15.75" customHeight="1" s="31"/>
+    <row r="143" ht="15.75" customHeight="1" s="31"/>
+    <row r="144" ht="15.75" customHeight="1" s="31"/>
+    <row r="145" ht="15.75" customHeight="1" s="31"/>
+    <row r="146" ht="15.75" customHeight="1" s="31"/>
+    <row r="147" ht="15.75" customHeight="1" s="31"/>
+    <row r="148" ht="15.75" customHeight="1" s="31"/>
+    <row r="149" ht="15.75" customHeight="1" s="31"/>
+    <row r="150" ht="15.75" customHeight="1" s="31"/>
+    <row r="151" ht="15.75" customHeight="1" s="31"/>
+    <row r="152" ht="15.75" customHeight="1" s="31"/>
+    <row r="153" ht="15.75" customHeight="1" s="31"/>
+    <row r="154" ht="15.75" customHeight="1" s="31"/>
+    <row r="155" ht="15.75" customHeight="1" s="31"/>
+    <row r="156" ht="15.75" customHeight="1" s="31"/>
+    <row r="157" ht="15.75" customHeight="1" s="31"/>
+    <row r="158" ht="15.75" customHeight="1" s="31"/>
+    <row r="159" ht="15.75" customHeight="1" s="31"/>
+    <row r="160" ht="15.75" customHeight="1" s="31"/>
+    <row r="161" ht="15.75" customHeight="1" s="31"/>
+    <row r="162" ht="15.75" customHeight="1" s="31"/>
+    <row r="163" ht="15.75" customHeight="1" s="31"/>
+    <row r="164" ht="15.75" customHeight="1" s="31"/>
+    <row r="165" ht="15.75" customHeight="1" s="31"/>
+    <row r="166" ht="15.75" customHeight="1" s="31"/>
+    <row r="167" ht="15.75" customHeight="1" s="31"/>
+    <row r="168" ht="15.75" customHeight="1" s="31"/>
+    <row r="169" ht="15.75" customHeight="1" s="31"/>
+    <row r="170" ht="15.75" customHeight="1" s="31"/>
+    <row r="171" ht="15.75" customHeight="1" s="31"/>
+    <row r="172" ht="15.75" customHeight="1" s="31"/>
+    <row r="173" ht="15.75" customHeight="1" s="31"/>
+    <row r="174" ht="15.75" customHeight="1" s="31"/>
+    <row r="175" ht="15.75" customHeight="1" s="31"/>
+    <row r="176" ht="15.75" customHeight="1" s="31"/>
+    <row r="177" ht="15.75" customHeight="1" s="31"/>
+    <row r="178" ht="15.75" customHeight="1" s="31"/>
+    <row r="179" ht="15.75" customHeight="1" s="31"/>
+    <row r="180" ht="15.75" customHeight="1" s="31"/>
+    <row r="181" ht="15.75" customHeight="1" s="31"/>
+    <row r="182" ht="15.75" customHeight="1" s="31"/>
+    <row r="183" ht="15.75" customHeight="1" s="31"/>
+    <row r="184" ht="15.75" customHeight="1" s="31"/>
+    <row r="185" ht="15.75" customHeight="1" s="31"/>
+    <row r="186" ht="15.75" customHeight="1" s="31"/>
+    <row r="187" ht="15.75" customHeight="1" s="31"/>
+    <row r="188" ht="15.75" customHeight="1" s="31"/>
+    <row r="189" ht="15.75" customHeight="1" s="31"/>
+    <row r="190" ht="15.75" customHeight="1" s="31"/>
+    <row r="191" ht="15.75" customHeight="1" s="31"/>
+    <row r="192" ht="15.75" customHeight="1" s="31"/>
+    <row r="193" ht="15.75" customHeight="1" s="31"/>
+    <row r="194" ht="15.75" customHeight="1" s="31"/>
+    <row r="195" ht="15.75" customHeight="1" s="31"/>
+    <row r="196" ht="15.75" customHeight="1" s="31"/>
+    <row r="197" ht="15.75" customHeight="1" s="31"/>
+    <row r="198" ht="15.75" customHeight="1" s="31"/>
+    <row r="199" ht="15.75" customHeight="1" s="31"/>
+    <row r="200" ht="15.75" customHeight="1" s="31"/>
+    <row r="201" ht="15.75" customHeight="1" s="31"/>
+    <row r="202" ht="15.75" customHeight="1" s="31"/>
+    <row r="203" ht="15.75" customHeight="1" s="31"/>
+    <row r="204" ht="15.75" customHeight="1" s="31"/>
+    <row r="205" ht="15.75" customHeight="1" s="31"/>
+    <row r="206" ht="15.75" customHeight="1" s="31"/>
+    <row r="207" ht="15.75" customHeight="1" s="31"/>
+    <row r="208" ht="15.75" customHeight="1" s="31"/>
+    <row r="209" ht="15.75" customHeight="1" s="31"/>
+    <row r="210" ht="15.75" customHeight="1" s="31"/>
+    <row r="211" ht="15.75" customHeight="1" s="31"/>
+    <row r="212" ht="15.75" customHeight="1" s="31"/>
+    <row r="213" ht="15.75" customHeight="1" s="31"/>
+    <row r="214" ht="15.75" customHeight="1" s="31"/>
+    <row r="215" ht="15.75" customHeight="1" s="31"/>
+    <row r="216" ht="15.75" customHeight="1" s="31"/>
+    <row r="217" ht="15.75" customHeight="1" s="31"/>
+    <row r="218" ht="15.75" customHeight="1" s="31"/>
+    <row r="219" ht="15.75" customHeight="1" s="31"/>
+    <row r="220" ht="15.75" customHeight="1" s="31"/>
+    <row r="221" ht="15.75" customHeight="1" s="31"/>
+    <row r="222" ht="15.75" customHeight="1" s="31"/>
+    <row r="223" ht="15.75" customHeight="1" s="31"/>
+    <row r="224" ht="15.75" customHeight="1" s="31"/>
+    <row r="225" ht="15.75" customHeight="1" s="31"/>
+    <row r="226" ht="15.75" customHeight="1" s="31"/>
+    <row r="227" ht="15.75" customHeight="1" s="31"/>
+    <row r="228" ht="15.75" customHeight="1" s="31"/>
+    <row r="229" ht="15.75" customHeight="1" s="31"/>
+    <row r="230" ht="15.75" customHeight="1" s="31"/>
+    <row r="231" ht="15.75" customHeight="1" s="31"/>
+    <row r="232" ht="15.75" customHeight="1" s="31"/>
+    <row r="233" ht="15.75" customHeight="1" s="31"/>
+    <row r="234" ht="15.75" customHeight="1" s="31"/>
+    <row r="235" ht="15.75" customHeight="1" s="31"/>
+    <row r="236" ht="15.75" customHeight="1" s="31"/>
+    <row r="237" ht="15.75" customHeight="1" s="31"/>
+    <row r="238" ht="15.75" customHeight="1" s="31"/>
+    <row r="239" ht="15.75" customHeight="1" s="31"/>
+    <row r="240" ht="15.75" customHeight="1" s="31"/>
+    <row r="241" ht="15.75" customHeight="1" s="31"/>
+    <row r="242" ht="15.75" customHeight="1" s="31"/>
+    <row r="243" ht="15.75" customHeight="1" s="31"/>
+    <row r="244" ht="15.75" customHeight="1" s="31"/>
+    <row r="245" ht="15.75" customHeight="1" s="31"/>
+    <row r="246" ht="15.75" customHeight="1" s="31"/>
+    <row r="247" ht="15.75" customHeight="1" s="31"/>
+    <row r="248" ht="15.75" customHeight="1" s="31"/>
+    <row r="249" ht="15.75" customHeight="1" s="31"/>
+    <row r="250" ht="15.75" customHeight="1" s="31"/>
+    <row r="251" ht="15.75" customHeight="1" s="31"/>
+    <row r="252" ht="15.75" customHeight="1" s="31"/>
+    <row r="253" ht="15.75" customHeight="1" s="31"/>
+    <row r="254" ht="15.75" customHeight="1" s="31"/>
+    <row r="255" ht="15.75" customHeight="1" s="31"/>
+    <row r="256" ht="15.75" customHeight="1" s="31"/>
+    <row r="257" ht="15.75" customHeight="1" s="31"/>
+    <row r="258" ht="15.75" customHeight="1" s="31"/>
+    <row r="259" ht="15.75" customHeight="1" s="31"/>
+    <row r="260" ht="15.75" customHeight="1" s="31"/>
+    <row r="261" ht="15.75" customHeight="1" s="31"/>
+    <row r="262" ht="15.75" customHeight="1" s="31"/>
+    <row r="263" ht="15.75" customHeight="1" s="31"/>
+    <row r="264" ht="15.75" customHeight="1" s="31"/>
+    <row r="265" ht="15.75" customHeight="1" s="31"/>
+    <row r="266" ht="15.75" customHeight="1" s="31"/>
+    <row r="267" ht="15.75" customHeight="1" s="31"/>
+    <row r="268" ht="15.75" customHeight="1" s="31"/>
+    <row r="269" ht="15.75" customHeight="1" s="31"/>
+    <row r="270" ht="15.75" customHeight="1" s="31"/>
+    <row r="271" ht="15.75" customHeight="1" s="31"/>
+    <row r="272" ht="15.75" customHeight="1" s="31"/>
+    <row r="273" ht="15.75" customHeight="1" s="31"/>
+    <row r="274" ht="15.75" customHeight="1" s="31"/>
+    <row r="275" ht="15.75" customHeight="1" s="31"/>
+    <row r="276" ht="15.75" customHeight="1" s="31"/>
+    <row r="277" ht="15.75" customHeight="1" s="31"/>
+    <row r="278" ht="15.75" customHeight="1" s="31"/>
+    <row r="279" ht="15.75" customHeight="1" s="31"/>
+    <row r="280" ht="15.75" customHeight="1" s="31"/>
+    <row r="281" ht="15.75" customHeight="1" s="31"/>
+    <row r="282" ht="15.75" customHeight="1" s="31"/>
+    <row r="283" ht="15.75" customHeight="1" s="31"/>
+    <row r="284" ht="15.75" customHeight="1" s="31"/>
+    <row r="285" ht="15.75" customHeight="1" s="31"/>
+    <row r="286" ht="15.75" customHeight="1" s="31"/>
+    <row r="287" ht="15.75" customHeight="1" s="31"/>
+    <row r="288" ht="15.75" customHeight="1" s="31"/>
+    <row r="289" ht="15.75" customHeight="1" s="31"/>
+    <row r="290" ht="15.75" customHeight="1" s="31"/>
+    <row r="291" ht="15.75" customHeight="1" s="31"/>
+    <row r="292" ht="15.75" customHeight="1" s="31"/>
+    <row r="293" ht="15.75" customHeight="1" s="31"/>
+    <row r="294" ht="15.75" customHeight="1" s="31"/>
+    <row r="295" ht="15.75" customHeight="1" s="31"/>
+    <row r="296" ht="15.75" customHeight="1" s="31"/>
+    <row r="297" ht="15.75" customHeight="1" s="31"/>
+    <row r="298" ht="15.75" customHeight="1" s="31"/>
+    <row r="299" ht="15.75" customHeight="1" s="31"/>
+    <row r="300" ht="15.75" customHeight="1" s="31"/>
+    <row r="301" ht="15.75" customHeight="1" s="31"/>
+    <row r="302" ht="15.75" customHeight="1" s="31"/>
+    <row r="303" ht="15.75" customHeight="1" s="31"/>
+    <row r="304" ht="15.75" customHeight="1" s="31"/>
+    <row r="305" ht="15.75" customHeight="1" s="31"/>
+    <row r="306" ht="15.75" customHeight="1" s="31"/>
+    <row r="307" ht="15.75" customHeight="1" s="31"/>
+    <row r="308" ht="15.75" customHeight="1" s="31"/>
+    <row r="309" ht="15.75" customHeight="1" s="31"/>
+    <row r="310" ht="15.75" customHeight="1" s="31"/>
+    <row r="311" ht="15.75" customHeight="1" s="31"/>
+    <row r="312" ht="15.75" customHeight="1" s="31"/>
+    <row r="313" ht="15.75" customHeight="1" s="31"/>
+    <row r="314" ht="15.75" customHeight="1" s="31"/>
+    <row r="315" ht="15.75" customHeight="1" s="31"/>
+    <row r="316" ht="15.75" customHeight="1" s="31"/>
+    <row r="317" ht="15.75" customHeight="1" s="31"/>
+    <row r="318" ht="15.75" customHeight="1" s="31"/>
+    <row r="319" ht="15.75" customHeight="1" s="31"/>
+    <row r="320" ht="15.75" customHeight="1" s="31"/>
+    <row r="321" ht="15.75" customHeight="1" s="31"/>
+    <row r="322" ht="15.75" customHeight="1" s="31"/>
+    <row r="323" ht="15.75" customHeight="1" s="31"/>
+    <row r="324" ht="15.75" customHeight="1" s="31"/>
+    <row r="325" ht="15.75" customHeight="1" s="31"/>
+    <row r="326" ht="15.75" customHeight="1" s="31"/>
+    <row r="327" ht="15.75" customHeight="1" s="31"/>
+    <row r="328" ht="15.75" customHeight="1" s="31"/>
+    <row r="329" ht="15.75" customHeight="1" s="31"/>
+    <row r="330" ht="15.75" customHeight="1" s="31"/>
+    <row r="331" ht="15.75" customHeight="1" s="31"/>
+    <row r="332" ht="15.75" customHeight="1" s="31"/>
+    <row r="333" ht="15.75" customHeight="1" s="31"/>
+    <row r="334" ht="15.75" customHeight="1" s="31"/>
+    <row r="335" ht="15.75" customHeight="1" s="31"/>
+    <row r="336" ht="15.75" customHeight="1" s="31"/>
+    <row r="337" ht="15.75" customHeight="1" s="31"/>
+    <row r="338" ht="15.75" customHeight="1" s="31"/>
+    <row r="339" ht="15.75" customHeight="1" s="31"/>
+    <row r="340" ht="15.75" customHeight="1" s="31"/>
+    <row r="341" ht="15.75" customHeight="1" s="31"/>
+    <row r="342" ht="15.75" customHeight="1" s="31"/>
+    <row r="343" ht="15.75" customHeight="1" s="31"/>
+    <row r="344" ht="15.75" customHeight="1" s="31"/>
+    <row r="345" ht="15.75" customHeight="1" s="31"/>
+    <row r="346" ht="15.75" customHeight="1" s="31"/>
+    <row r="347" ht="15.75" customHeight="1" s="31"/>
+    <row r="348" ht="15.75" customHeight="1" s="31"/>
+    <row r="349" ht="15.75" customHeight="1" s="31"/>
+    <row r="350" ht="15.75" customHeight="1" s="31"/>
+    <row r="351" ht="15.75" customHeight="1" s="31"/>
+    <row r="352" ht="15.75" customHeight="1" s="31"/>
+    <row r="353" ht="15.75" customHeight="1" s="31"/>
+    <row r="354" ht="15.75" customHeight="1" s="31"/>
+    <row r="355" ht="15.75" customHeight="1" s="31"/>
+    <row r="356" ht="15.75" customHeight="1" s="31"/>
+    <row r="357" ht="15.75" customHeight="1" s="31"/>
+    <row r="358" ht="15.75" customHeight="1" s="31"/>
+    <row r="359" ht="15.75" customHeight="1" s="31"/>
+    <row r="360" ht="15.75" customHeight="1" s="31"/>
+    <row r="361" ht="15.75" customHeight="1" s="31"/>
+    <row r="362" ht="15.75" customHeight="1" s="31"/>
+    <row r="363" ht="15.75" customHeight="1" s="31"/>
+    <row r="364" ht="15.75" customHeight="1" s="31"/>
+    <row r="365" ht="15.75" customHeight="1" s="31"/>
+    <row r="366" ht="15.75" customHeight="1" s="31"/>
+    <row r="367" ht="15.75" customHeight="1" s="31"/>
+    <row r="368" ht="15.75" customHeight="1" s="31"/>
+    <row r="369" ht="15.75" customHeight="1" s="31"/>
+    <row r="370" ht="15.75" customHeight="1" s="31"/>
+    <row r="371" ht="15.75" customHeight="1" s="31"/>
+    <row r="372" ht="15.75" customHeight="1" s="31"/>
+    <row r="373" ht="15.75" customHeight="1" s="31"/>
+    <row r="374" ht="15.75" customHeight="1" s="31"/>
+    <row r="375" ht="15.75" customHeight="1" s="31"/>
+    <row r="376" ht="15.75" customHeight="1" s="31"/>
+    <row r="377" ht="15.75" customHeight="1" s="31"/>
+    <row r="378" ht="15.75" customHeight="1" s="31"/>
+    <row r="379" ht="15.75" customHeight="1" s="31"/>
+    <row r="380" ht="15.75" customHeight="1" s="31"/>
+    <row r="381" ht="15.75" customHeight="1" s="31"/>
+    <row r="382" ht="15.75" customHeight="1" s="31"/>
+    <row r="383" ht="15.75" customHeight="1" s="31"/>
+    <row r="384" ht="15.75" customHeight="1" s="31"/>
+    <row r="385" ht="15.75" customHeight="1" s="31"/>
+    <row r="386" ht="15.75" customHeight="1" s="31"/>
+    <row r="387" ht="15.75" customHeight="1" s="31"/>
+    <row r="388" ht="15.75" customHeight="1" s="31"/>
+    <row r="389" ht="15.75" customHeight="1" s="31"/>
+    <row r="390" ht="15.75" customHeight="1" s="31"/>
+    <row r="391" ht="15.75" customHeight="1" s="31"/>
+    <row r="392" ht="15.75" customHeight="1" s="31"/>
+    <row r="393" ht="15.75" customHeight="1" s="31"/>
+    <row r="394" ht="15.75" customHeight="1" s="31"/>
+    <row r="395" ht="15.75" customHeight="1" s="31"/>
+    <row r="396" ht="15.75" customHeight="1" s="31"/>
+    <row r="397" ht="15.75" customHeight="1" s="31"/>
+    <row r="398" ht="15.75" customHeight="1" s="31"/>
+    <row r="399" ht="15.75" customHeight="1" s="31"/>
+    <row r="400" ht="15.75" customHeight="1" s="31"/>
+    <row r="401" ht="15.75" customHeight="1" s="31"/>
+    <row r="402" ht="15.75" customHeight="1" s="31"/>
+    <row r="403" ht="15.75" customHeight="1" s="31"/>
+    <row r="404" ht="15.75" customHeight="1" s="31"/>
+    <row r="405" ht="15.75" customHeight="1" s="31"/>
+    <row r="406" ht="15.75" customHeight="1" s="31"/>
+    <row r="407" ht="15.75" customHeight="1" s="31"/>
+    <row r="408" ht="15.75" customHeight="1" s="31"/>
+    <row r="409" ht="15.75" customHeight="1" s="31"/>
+    <row r="410" ht="15.75" customHeight="1" s="31"/>
+    <row r="411" ht="15.75" customHeight="1" s="31"/>
+    <row r="412" ht="15.75" customHeight="1" s="31"/>
+    <row r="413" ht="15.75" customHeight="1" s="31"/>
+    <row r="414" ht="15.75" customHeight="1" s="31"/>
+    <row r="415" ht="15.75" customHeight="1" s="31"/>
+    <row r="416" ht="15.75" customHeight="1" s="31"/>
+    <row r="417" ht="15.75" customHeight="1" s="31"/>
+    <row r="418" ht="15.75" customHeight="1" s="31"/>
+    <row r="419" ht="15.75" customHeight="1" s="31"/>
+    <row r="420" ht="15.75" customHeight="1" s="31"/>
+    <row r="421" ht="15.75" customHeight="1" s="31"/>
+    <row r="422" ht="15.75" customHeight="1" s="31"/>
+    <row r="423" ht="15.75" customHeight="1" s="31"/>
+    <row r="424" ht="15.75" customHeight="1" s="31"/>
+    <row r="425" ht="15.75" customHeight="1" s="31"/>
+    <row r="426" ht="15.75" customHeight="1" s="31"/>
+    <row r="427" ht="15.75" customHeight="1" s="31"/>
+    <row r="428" ht="15.75" customHeight="1" s="31"/>
+    <row r="429" ht="15.75" customHeight="1" s="31"/>
+    <row r="430" ht="15.75" customHeight="1" s="31"/>
+    <row r="431" ht="15.75" customHeight="1" s="31"/>
+    <row r="432" ht="15.75" customHeight="1" s="31"/>
+    <row r="433" ht="15.75" customHeight="1" s="31"/>
+    <row r="434" ht="15.75" customHeight="1" s="31"/>
+    <row r="435" ht="15.75" customHeight="1" s="31"/>
+    <row r="436" ht="15.75" customHeight="1" s="31"/>
+    <row r="437" ht="15.75" customHeight="1" s="31"/>
+    <row r="438" ht="15.75" customHeight="1" s="31"/>
+    <row r="439" ht="15.75" customHeight="1" s="31"/>
+    <row r="440" ht="15.75" customHeight="1" s="31"/>
+    <row r="441" ht="15.75" customHeight="1" s="31"/>
+    <row r="442" ht="15.75" customHeight="1" s="31"/>
+    <row r="443" ht="15.75" customHeight="1" s="31"/>
+    <row r="444" ht="15.75" customHeight="1" s="31"/>
+    <row r="445" ht="15.75" customHeight="1" s="31"/>
+    <row r="446" ht="15.75" customHeight="1" s="31"/>
+    <row r="447" ht="15.75" customHeight="1" s="31"/>
+    <row r="448" ht="15.75" customHeight="1" s="31"/>
+    <row r="449" ht="15.75" customHeight="1" s="31"/>
+    <row r="450" ht="15.75" customHeight="1" s="31"/>
+    <row r="451" ht="15.75" customHeight="1" s="31"/>
+    <row r="452" ht="15.75" customHeight="1" s="31"/>
+    <row r="453" ht="15.75" customHeight="1" s="31"/>
+    <row r="454" ht="15.75" customHeight="1" s="31"/>
+    <row r="455" ht="15.75" customHeight="1" s="31"/>
+    <row r="456" ht="15.75" customHeight="1" s="31"/>
+    <row r="457" ht="15.75" customHeight="1" s="31"/>
+    <row r="458" ht="15.75" customHeight="1" s="31"/>
+    <row r="459" ht="15.75" customHeight="1" s="31"/>
+    <row r="460" ht="15.75" customHeight="1" s="31"/>
+    <row r="461" ht="15.75" customHeight="1" s="31"/>
+    <row r="462" ht="15.75" customHeight="1" s="31"/>
+    <row r="463" ht="15.75" customHeight="1" s="31"/>
+    <row r="464" ht="15.75" customHeight="1" s="31"/>
+    <row r="465" ht="15.75" customHeight="1" s="31"/>
+    <row r="466" ht="15.75" customHeight="1" s="31"/>
+    <row r="467" ht="15.75" customHeight="1" s="31"/>
+    <row r="468" ht="15.75" customHeight="1" s="31"/>
+    <row r="469" ht="15.75" customHeight="1" s="31"/>
+    <row r="470" ht="15.75" customHeight="1" s="31"/>
+    <row r="471" ht="15.75" customHeight="1" s="31"/>
+    <row r="472" ht="15.75" customHeight="1" s="31"/>
+    <row r="473" ht="15.75" customHeight="1" s="31"/>
+    <row r="474" ht="15.75" customHeight="1" s="31"/>
+    <row r="475" ht="15.75" customHeight="1" s="31"/>
+    <row r="476" ht="15.75" customHeight="1" s="31"/>
+    <row r="477" ht="15.75" customHeight="1" s="31"/>
+    <row r="478" ht="15.75" customHeight="1" s="31"/>
+    <row r="479" ht="15.75" customHeight="1" s="31"/>
+    <row r="480" ht="15.75" customHeight="1" s="31"/>
+    <row r="481" ht="15.75" customHeight="1" s="31"/>
+    <row r="482" ht="15.75" customHeight="1" s="31"/>
+    <row r="483" ht="15.75" customHeight="1" s="31"/>
+    <row r="484" ht="15.75" customHeight="1" s="31"/>
+    <row r="485" ht="15.75" customHeight="1" s="31"/>
+    <row r="486" ht="15.75" customHeight="1" s="31"/>
+    <row r="487" ht="15.75" customHeight="1" s="31"/>
+    <row r="488" ht="15.75" customHeight="1" s="31"/>
+    <row r="489" ht="15.75" customHeight="1" s="31"/>
+    <row r="490" ht="15.75" customHeight="1" s="31"/>
+    <row r="491" ht="15.75" customHeight="1" s="31"/>
+    <row r="492" ht="15.75" customHeight="1" s="31"/>
+    <row r="493" ht="15.75" customHeight="1" s="31"/>
+    <row r="494" ht="15.75" customHeight="1" s="31"/>
+    <row r="495" ht="15.75" customHeight="1" s="31"/>
+    <row r="496" ht="15.75" customHeight="1" s="31"/>
+    <row r="497" ht="15.75" customHeight="1" s="31"/>
+    <row r="498" ht="15.75" customHeight="1" s="31"/>
+    <row r="499" ht="15.75" customHeight="1" s="31"/>
+    <row r="500" ht="15.75" customHeight="1" s="31"/>
+    <row r="501" ht="15.75" customHeight="1" s="31"/>
+    <row r="502" ht="15.75" customHeight="1" s="31"/>
+    <row r="503" ht="15.75" customHeight="1" s="31"/>
+    <row r="504" ht="15.75" customHeight="1" s="31"/>
+    <row r="505" ht="15.75" customHeight="1" s="31"/>
+    <row r="506" ht="15.75" customHeight="1" s="31"/>
+    <row r="507" ht="15.75" customHeight="1" s="31"/>
+    <row r="508" ht="15.75" customHeight="1" s="31"/>
+    <row r="509" ht="15.75" customHeight="1" s="31"/>
+    <row r="510" ht="15.75" customHeight="1" s="31"/>
+    <row r="511" ht="15.75" customHeight="1" s="31"/>
+    <row r="512" ht="15.75" customHeight="1" s="31"/>
+    <row r="513" ht="15.75" customHeight="1" s="31"/>
+    <row r="514" ht="15.75" customHeight="1" s="31"/>
+    <row r="515" ht="15.75" customHeight="1" s="31"/>
+    <row r="516" ht="15.75" customHeight="1" s="31"/>
+    <row r="517" ht="15.75" customHeight="1" s="31"/>
+    <row r="518" ht="15.75" customHeight="1" s="31"/>
+    <row r="519" ht="15.75" customHeight="1" s="31"/>
+    <row r="520" ht="15.75" customHeight="1" s="31"/>
+    <row r="521" ht="15.75" customHeight="1" s="31"/>
+    <row r="522" ht="15.75" customHeight="1" s="31"/>
+    <row r="523" ht="15.75" customHeight="1" s="31"/>
+    <row r="524" ht="15.75" customHeight="1" s="31"/>
+    <row r="525" ht="15.75" customHeight="1" s="31"/>
+    <row r="526" ht="15.75" customHeight="1" s="31"/>
+    <row r="527" ht="15.75" customHeight="1" s="31"/>
+    <row r="528" ht="15.75" customHeight="1" s="31"/>
+    <row r="529" ht="15.75" customHeight="1" s="31"/>
+    <row r="530" ht="15.75" customHeight="1" s="31"/>
+    <row r="531" ht="15.75" customHeight="1" s="31"/>
+    <row r="532" ht="15.75" customHeight="1" s="31"/>
+    <row r="533" ht="15.75" customHeight="1" s="31"/>
+    <row r="534" ht="15.75" customHeight="1" s="31"/>
+    <row r="535" ht="15.75" customHeight="1" s="31"/>
+    <row r="536" ht="15.75" customHeight="1" s="31"/>
+    <row r="537" ht="15.75" customHeight="1" s="31"/>
+    <row r="538" ht="15.75" customHeight="1" s="31"/>
+    <row r="539" ht="15.75" customHeight="1" s="31"/>
+    <row r="540" ht="15.75" customHeight="1" s="31"/>
+    <row r="541" ht="15.75" customHeight="1" s="31"/>
+    <row r="542" ht="15.75" customHeight="1" s="31"/>
+    <row r="543" ht="15.75" customHeight="1" s="31"/>
+    <row r="544" ht="15.75" customHeight="1" s="31"/>
+    <row r="545" ht="15.75" customHeight="1" s="31"/>
+    <row r="546" ht="15.75" customHeight="1" s="31"/>
+    <row r="547" ht="15.75" customHeight="1" s="31"/>
+    <row r="548" ht="15.75" customHeight="1" s="31"/>
+    <row r="549" ht="15.75" customHeight="1" s="31"/>
+    <row r="550" ht="15.75" customHeight="1" s="31"/>
+    <row r="551" ht="15.75" customHeight="1" s="31"/>
+    <row r="552" ht="15.75" customHeight="1" s="31"/>
+    <row r="553" ht="15.75" customHeight="1" s="31"/>
+    <row r="554" ht="15.75" customHeight="1" s="31"/>
+    <row r="555" ht="15.75" customHeight="1" s="31"/>
+    <row r="556" ht="15.75" customHeight="1" s="31"/>
+    <row r="557" ht="15.75" customHeight="1" s="31"/>
+    <row r="558" ht="15.75" customHeight="1" s="31"/>
+    <row r="559" ht="15.75" customHeight="1" s="31"/>
+    <row r="560" ht="15.75" customHeight="1" s="31"/>
+    <row r="561" ht="15.75" customHeight="1" s="31"/>
+    <row r="562" ht="15.75" customHeight="1" s="31"/>
+    <row r="563" ht="15.75" customHeight="1" s="31"/>
+    <row r="564" ht="15.75" customHeight="1" s="31"/>
+    <row r="565" ht="15.75" customHeight="1" s="31"/>
+    <row r="566" ht="15.75" customHeight="1" s="31"/>
+    <row r="567" ht="15.75" customHeight="1" s="31"/>
+    <row r="568" ht="15.75" customHeight="1" s="31"/>
+    <row r="569" ht="15.75" customHeight="1" s="31"/>
+    <row r="570" ht="15.75" customHeight="1" s="31"/>
+    <row r="571" ht="15.75" customHeight="1" s="31"/>
+    <row r="572" ht="15.75" customHeight="1" s="31"/>
+    <row r="573" ht="15.75" customHeight="1" s="31"/>
+    <row r="574" ht="15.75" customHeight="1" s="31"/>
+    <row r="575" ht="15.75" customHeight="1" s="31"/>
+    <row r="576" ht="15.75" customHeight="1" s="31"/>
+    <row r="577" ht="15.75" customHeight="1" s="31"/>
+    <row r="578" ht="15.75" customHeight="1" s="31"/>
+    <row r="579" ht="15.75" customHeight="1" s="31"/>
+    <row r="580" ht="15.75" customHeight="1" s="31"/>
+    <row r="581" ht="15.75" customHeight="1" s="31"/>
+    <row r="582" ht="15.75" customHeight="1" s="31"/>
+    <row r="583" ht="15.75" customHeight="1" s="31"/>
+    <row r="584" ht="15.75" customHeight="1" s="31"/>
+    <row r="585" ht="15.75" customHeight="1" s="31"/>
+    <row r="586" ht="15.75" customHeight="1" s="31"/>
+    <row r="587" ht="15.75" customHeight="1" s="31"/>
+    <row r="588" ht="15.75" customHeight="1" s="31"/>
+    <row r="589" ht="15.75" customHeight="1" s="31"/>
+    <row r="590" ht="15.75" customHeight="1" s="31"/>
+    <row r="591" ht="15.75" customHeight="1" s="31"/>
+    <row r="592" ht="15.75" customHeight="1" s="31"/>
+    <row r="593" ht="15.75" customHeight="1" s="31"/>
+    <row r="594" ht="15.75" customHeight="1" s="31"/>
+    <row r="595" ht="15.75" customHeight="1" s="31"/>
+    <row r="596" ht="15.75" customHeight="1" s="31"/>
+    <row r="597" ht="15.75" customHeight="1" s="31"/>
+    <row r="598" ht="15.75" customHeight="1" s="31"/>
+    <row r="599" ht="15.75" customHeight="1" s="31"/>
+    <row r="600" ht="15.75" customHeight="1" s="31"/>
+    <row r="601" ht="15.75" customHeight="1" s="31"/>
+    <row r="602" ht="15.75" customHeight="1" s="31"/>
+    <row r="603" ht="15.75" customHeight="1" s="31"/>
+    <row r="604" ht="15.75" customHeight="1" s="31"/>
+    <row r="605" ht="15.75" customHeight="1" s="31"/>
+    <row r="606" ht="15.75" customHeight="1" s="31"/>
+    <row r="607" ht="15.75" customHeight="1" s="31"/>
+    <row r="608" ht="15.75" customHeight="1" s="31"/>
+    <row r="609" ht="15.75" customHeight="1" s="31"/>
+    <row r="610" ht="15.75" customHeight="1" s="31"/>
+    <row r="611" ht="15.75" customHeight="1" s="31"/>
+    <row r="612" ht="15.75" customHeight="1" s="31"/>
+    <row r="613" ht="15.75" customHeight="1" s="31"/>
+    <row r="614" ht="15.75" customHeight="1" s="31"/>
+    <row r="615" ht="15.75" customHeight="1" s="31"/>
+    <row r="616" ht="15.75" customHeight="1" s="31"/>
+    <row r="617" ht="15.75" customHeight="1" s="31"/>
+    <row r="618" ht="15.75" customHeight="1" s="31"/>
+    <row r="619" ht="15.75" customHeight="1" s="31"/>
+    <row r="620" ht="15.75" customHeight="1" s="31"/>
+    <row r="621" ht="15.75" customHeight="1" s="31"/>
+    <row r="622" ht="15.75" customHeight="1" s="31"/>
+    <row r="623" ht="15.75" customHeight="1" s="31"/>
+    <row r="624" ht="15.75" customHeight="1" s="31"/>
+    <row r="625" ht="15.75" customHeight="1" s="31"/>
+    <row r="626" ht="15.75" customHeight="1" s="31"/>
+    <row r="627" ht="15.75" customHeight="1" s="31"/>
+    <row r="628" ht="15.75" customHeight="1" s="31"/>
+    <row r="629" ht="15.75" customHeight="1" s="31"/>
+    <row r="630" ht="15.75" customHeight="1" s="31"/>
+    <row r="631" ht="15.75" customHeight="1" s="31"/>
+    <row r="632" ht="15.75" customHeight="1" s="31"/>
+    <row r="633" ht="15.75" customHeight="1" s="31"/>
+    <row r="634" ht="15.75" customHeight="1" s="31"/>
+    <row r="635" ht="15.75" customHeight="1" s="31"/>
+    <row r="636" ht="15.75" customHeight="1" s="31"/>
+    <row r="637" ht="15.75" customHeight="1" s="31"/>
+    <row r="638" ht="15.75" customHeight="1" s="31"/>
+    <row r="639" ht="15.75" customHeight="1" s="31"/>
+    <row r="640" ht="15.75" customHeight="1" s="31"/>
+    <row r="641" ht="15.75" customHeight="1" s="31"/>
+    <row r="642" ht="15.75" customHeight="1" s="31"/>
+    <row r="643" ht="15.75" customHeight="1" s="31"/>
+    <row r="644" ht="15.75" customHeight="1" s="31"/>
+    <row r="645" ht="15.75" customHeight="1" s="31"/>
+    <row r="646" ht="15.75" customHeight="1" s="31"/>
+    <row r="647" ht="15.75" customHeight="1" s="31"/>
+    <row r="648" ht="15.75" customHeight="1" s="31"/>
+    <row r="649" ht="15.75" customHeight="1" s="31"/>
+    <row r="650" ht="15.75" customHeight="1" s="31"/>
+    <row r="651" ht="15.75" customHeight="1" s="31"/>
+    <row r="652" ht="15.75" customHeight="1" s="31"/>
+    <row r="653" ht="15.75" customHeight="1" s="31"/>
+    <row r="654" ht="15.75" customHeight="1" s="31"/>
+    <row r="655" ht="15.75" customHeight="1" s="31"/>
+    <row r="656" ht="15.75" customHeight="1" s="31"/>
+    <row r="657" ht="15.75" customHeight="1" s="31"/>
+    <row r="658" ht="15.75" customHeight="1" s="31"/>
+    <row r="659" ht="15.75" customHeight="1" s="31"/>
+    <row r="660" ht="15.75" customHeight="1" s="31"/>
+    <row r="661" ht="15.75" customHeight="1" s="31"/>
+    <row r="662" ht="15.75" customHeight="1" s="31"/>
+    <row r="663" ht="15.75" customHeight="1" s="31"/>
+    <row r="664" ht="15.75" customHeight="1" s="31"/>
+    <row r="665" ht="15.75" customHeight="1" s="31"/>
+    <row r="666" ht="15.75" customHeight="1" s="31"/>
+    <row r="667" ht="15.75" customHeight="1" s="31"/>
+    <row r="668" ht="15.75" customHeight="1" s="31"/>
+    <row r="669" ht="15.75" customHeight="1" s="31"/>
+    <row r="670" ht="15.75" customHeight="1" s="31"/>
+    <row r="671" ht="15.75" customHeight="1" s="31"/>
+    <row r="672" ht="15.75" customHeight="1" s="31"/>
+    <row r="673" ht="15.75" customHeight="1" s="31"/>
+    <row r="674" ht="15.75" customHeight="1" s="31"/>
+    <row r="675" ht="15.75" customHeight="1" s="31"/>
+    <row r="676" ht="15.75" customHeight="1" s="31"/>
+    <row r="677" ht="15.75" customHeight="1" s="31"/>
+    <row r="678" ht="15.75" customHeight="1" s="31"/>
+    <row r="679" ht="15.75" customHeight="1" s="31"/>
+    <row r="680" ht="15.75" customHeight="1" s="31"/>
+    <row r="681" ht="15.75" customHeight="1" s="31"/>
+    <row r="682" ht="15.75" customHeight="1" s="31"/>
+    <row r="683" ht="15.75" customHeight="1" s="31"/>
+    <row r="684" ht="15.75" customHeight="1" s="31"/>
+    <row r="685" ht="15.75" customHeight="1" s="31"/>
+    <row r="686" ht="15.75" customHeight="1" s="31"/>
+    <row r="687" ht="15.75" customHeight="1" s="31"/>
+    <row r="688" ht="15.75" customHeight="1" s="31"/>
+    <row r="689" ht="15.75" customHeight="1" s="31"/>
+    <row r="690" ht="15.75" customHeight="1" s="31"/>
+    <row r="691" ht="15.75" customHeight="1" s="31"/>
+    <row r="692" ht="15.75" customHeight="1" s="31"/>
+    <row r="693" ht="15.75" customHeight="1" s="31"/>
+    <row r="694" ht="15.75" customHeight="1" s="31"/>
+    <row r="695" ht="15.75" customHeight="1" s="31"/>
+    <row r="696" ht="15.75" customHeight="1" s="31"/>
+    <row r="697" ht="15.75" customHeight="1" s="31"/>
+    <row r="698" ht="15.75" customHeight="1" s="31"/>
+    <row r="699" ht="15.75" customHeight="1" s="31"/>
+    <row r="700" ht="15.75" customHeight="1" s="31"/>
+    <row r="701" ht="15.75" customHeight="1" s="31"/>
+    <row r="702" ht="15.75" customHeight="1" s="31"/>
+    <row r="703" ht="15.75" customHeight="1" s="31"/>
+    <row r="704" ht="15.75" customHeight="1" s="31"/>
+    <row r="705" ht="15.75" customHeight="1" s="31"/>
+    <row r="706" ht="15.75" customHeight="1" s="31"/>
+    <row r="707" ht="15.75" customHeight="1" s="31"/>
+    <row r="708" ht="15.75" customHeight="1" s="31"/>
+    <row r="709" ht="15.75" customHeight="1" s="31"/>
+    <row r="710" ht="15.75" customHeight="1" s="31"/>
+    <row r="711" ht="15.75" customHeight="1" s="31"/>
+    <row r="712" ht="15.75" customHeight="1" s="31"/>
+    <row r="713" ht="15.75" customHeight="1" s="31"/>
+    <row r="714" ht="15.75" customHeight="1" s="31"/>
+    <row r="715" ht="15.75" customHeight="1" s="31"/>
+    <row r="716" ht="15.75" customHeight="1" s="31"/>
+    <row r="717" ht="15.75" customHeight="1" s="31"/>
+    <row r="718" ht="15.75" customHeight="1" s="31"/>
+    <row r="719" ht="15.75" customHeight="1" s="31"/>
+    <row r="720" ht="15.75" customHeight="1" s="31"/>
+    <row r="721" ht="15.75" customHeight="1" s="31"/>
+    <row r="722" ht="15.75" customHeight="1" s="31"/>
+    <row r="723" ht="15.75" customHeight="1" s="31"/>
+    <row r="724" ht="15.75" customHeight="1" s="31"/>
+    <row r="725" ht="15.75" customHeight="1" s="31"/>
+    <row r="726" ht="15.75" customHeight="1" s="31"/>
+    <row r="727" ht="15.75" customHeight="1" s="31"/>
+    <row r="728" ht="15.75" customHeight="1" s="31"/>
+    <row r="729" ht="15.75" customHeight="1" s="31"/>
+    <row r="730" ht="15.75" customHeight="1" s="31"/>
+    <row r="731" ht="15.75" customHeight="1" s="31"/>
+    <row r="732" ht="15.75" customHeight="1" s="31"/>
+    <row r="733" ht="15.75" customHeight="1" s="31"/>
+    <row r="734" ht="15.75" customHeight="1" s="31"/>
+    <row r="735" ht="15.75" customHeight="1" s="31"/>
+    <row r="736" ht="15.75" customHeight="1" s="31"/>
+    <row r="737" ht="15.75" customHeight="1" s="31"/>
+    <row r="738" ht="15.75" customHeight="1" s="31"/>
+    <row r="739" ht="15.75" customHeight="1" s="31"/>
+    <row r="740" ht="15.75" customHeight="1" s="31"/>
+    <row r="741" ht="15.75" customHeight="1" s="31"/>
+    <row r="742" ht="15.75" customHeight="1" s="31"/>
+    <row r="743" ht="15.75" customHeight="1" s="31"/>
+    <row r="744" ht="15.75" customHeight="1" s="31"/>
+    <row r="745" ht="15.75" customHeight="1" s="31"/>
+    <row r="746" ht="15.75" customHeight="1" s="31"/>
+    <row r="747" ht="15.75" customHeight="1" s="31"/>
+    <row r="748" ht="15.75" customHeight="1" s="31"/>
+    <row r="749" ht="15.75" customHeight="1" s="31"/>
+    <row r="750" ht="15.75" customHeight="1" s="31"/>
+    <row r="751" ht="15.75" customHeight="1" s="31"/>
+    <row r="752" ht="15.75" customHeight="1" s="31"/>
+    <row r="753" ht="15.75" customHeight="1" s="31"/>
+    <row r="754" ht="15.75" customHeight="1" s="31"/>
+    <row r="755" ht="15.75" customHeight="1" s="31"/>
+    <row r="756" ht="15.75" customHeight="1" s="31"/>
+    <row r="757" ht="15.75" customHeight="1" s="31"/>
+    <row r="758" ht="15.75" customHeight="1" s="31"/>
+    <row r="759" ht="15.75" customHeight="1" s="31"/>
+    <row r="760" ht="15.75" customHeight="1" s="31"/>
+    <row r="761" ht="15.75" customHeight="1" s="31"/>
+    <row r="762" ht="15.75" customHeight="1" s="31"/>
+    <row r="763" ht="15.75" customHeight="1" s="31"/>
+    <row r="764" ht="15.75" customHeight="1" s="31"/>
+    <row r="765" ht="15.75" customHeight="1" s="31"/>
+    <row r="766" ht="15.75" customHeight="1" s="31"/>
+    <row r="767" ht="15.75" customHeight="1" s="31"/>
+    <row r="768" ht="15.75" customHeight="1" s="31"/>
+    <row r="769" ht="15.75" customHeight="1" s="31"/>
+    <row r="770" ht="15.75" customHeight="1" s="31"/>
+    <row r="771" ht="15.75" customHeight="1" s="31"/>
+    <row r="772" ht="15.75" customHeight="1" s="31"/>
+    <row r="773" ht="15.75" customHeight="1" s="31"/>
+    <row r="774" ht="15.75" customHeight="1" s="31"/>
+    <row r="775" ht="15.75" customHeight="1" s="31"/>
+    <row r="776" ht="15.75" customHeight="1" s="31"/>
+    <row r="777" ht="15.75" customHeight="1" s="31"/>
+    <row r="778" ht="15.75" customHeight="1" s="31"/>
+    <row r="779" ht="15.75" customHeight="1" s="31"/>
+    <row r="780" ht="15.75" customHeight="1" s="31"/>
+    <row r="781" ht="15.75" customHeight="1" s="31"/>
+    <row r="782" ht="15.75" customHeight="1" s="31"/>
+    <row r="783" ht="15.75" customHeight="1" s="31"/>
+    <row r="784" ht="15.75" customHeight="1" s="31"/>
+    <row r="785" ht="15.75" customHeight="1" s="31"/>
+    <row r="786" ht="15.75" customHeight="1" s="31"/>
+    <row r="787" ht="15.75" customHeight="1" s="31"/>
+    <row r="788" ht="15.75" customHeight="1" s="31"/>
+    <row r="789" ht="15.75" customHeight="1" s="31"/>
+    <row r="790" ht="15.75" customHeight="1" s="31"/>
+    <row r="791" ht="15.75" customHeight="1" s="31"/>
+    <row r="792" ht="15.75" customHeight="1" s="31"/>
+    <row r="793" ht="15.75" customHeight="1" s="31"/>
+    <row r="794" ht="15.75" customHeight="1" s="31"/>
+    <row r="795" ht="15.75" customHeight="1" s="31"/>
+    <row r="796" ht="15.75" customHeight="1" s="31"/>
+    <row r="797" ht="15.75" customHeight="1" s="31"/>
+    <row r="798" ht="15.75" customHeight="1" s="31"/>
+    <row r="799" ht="15.75" customHeight="1" s="31"/>
+    <row r="800" ht="15.75" customHeight="1" s="31"/>
+    <row r="801" ht="15.75" customHeight="1" s="31"/>
+    <row r="802" ht="15.75" customHeight="1" s="31"/>
+    <row r="803" ht="15.75" customHeight="1" s="31"/>
+    <row r="804" ht="15.75" customHeight="1" s="31"/>
+    <row r="805" ht="15.75" customHeight="1" s="31"/>
+    <row r="806" ht="15.75" customHeight="1" s="31"/>
+    <row r="807" ht="15.75" customHeight="1" s="31"/>
+    <row r="808" ht="15.75" customHeight="1" s="31"/>
+    <row r="809" ht="15.75" customHeight="1" s="31"/>
+    <row r="810" ht="15.75" customHeight="1" s="31"/>
+    <row r="811" ht="15.75" customHeight="1" s="31"/>
+    <row r="812" ht="15.75" customHeight="1" s="31"/>
+    <row r="813" ht="15.75" customHeight="1" s="31"/>
+    <row r="814" ht="15.75" customHeight="1" s="31"/>
+    <row r="815" ht="15.75" customHeight="1" s="31"/>
+    <row r="816" ht="15.75" customHeight="1" s="31"/>
+    <row r="817" ht="15.75" customHeight="1" s="31"/>
+    <row r="818" ht="15.75" customHeight="1" s="31"/>
+    <row r="819" ht="15.75" customHeight="1" s="31"/>
+    <row r="820" ht="15.75" customHeight="1" s="31"/>
+    <row r="821" ht="15.75" customHeight="1" s="31"/>
+    <row r="822" ht="15.75" customHeight="1" s="31"/>
+    <row r="823" ht="15.75" customHeight="1" s="31"/>
+    <row r="824" ht="15.75" customHeight="1" s="31"/>
+    <row r="825" ht="15.75" customHeight="1" s="31"/>
+    <row r="826" ht="15.75" customHeight="1" s="31"/>
+    <row r="827" ht="15.75" customHeight="1" s="31"/>
+    <row r="828" ht="15.75" customHeight="1" s="31"/>
+    <row r="829" ht="15.75" customHeight="1" s="31"/>
+    <row r="830" ht="15.75" customHeight="1" s="31"/>
+    <row r="831" ht="15.75" customHeight="1" s="31"/>
+    <row r="832" ht="15.75" customHeight="1" s="31"/>
+    <row r="833" ht="15.75" customHeight="1" s="31"/>
+    <row r="834" ht="15.75" customHeight="1" s="31"/>
+    <row r="835" ht="15.75" customHeight="1" s="31"/>
+    <row r="836" ht="15.75" customHeight="1" s="31"/>
+    <row r="837" ht="15.75" customHeight="1" s="31"/>
+    <row r="838" ht="15.75" customHeight="1" s="31"/>
+    <row r="839" ht="15.75" customHeight="1" s="31"/>
+    <row r="840" ht="15.75" customHeight="1" s="31"/>
+    <row r="841" ht="15.75" customHeight="1" s="31"/>
+    <row r="842" ht="15.75" customHeight="1" s="31"/>
+    <row r="843" ht="15.75" customHeight="1" s="31"/>
+    <row r="844" ht="15.75" customHeight="1" s="31"/>
+    <row r="845" ht="15.75" customHeight="1" s="31"/>
+    <row r="846" ht="15.75" customHeight="1" s="31"/>
+    <row r="847" ht="15.75" customHeight="1" s="31"/>
+    <row r="848" ht="15.75" customHeight="1" s="31"/>
+    <row r="849" ht="15.75" customHeight="1" s="31"/>
+    <row r="850" ht="15.75" customHeight="1" s="31"/>
+    <row r="851" ht="15.75" customHeight="1" s="31"/>
+    <row r="852" ht="15.75" customHeight="1" s="31"/>
+    <row r="853" ht="15.75" customHeight="1" s="31"/>
+    <row r="854" ht="15.75" customHeight="1" s="31"/>
+    <row r="855" ht="15.75" customHeight="1" s="31"/>
+    <row r="856" ht="15.75" customHeight="1" s="31"/>
+    <row r="857" ht="15.75" customHeight="1" s="31"/>
+    <row r="858" ht="15.75" customHeight="1" s="31"/>
+    <row r="859" ht="15.75" customHeight="1" s="31"/>
+    <row r="860" ht="15.75" customHeight="1" s="31"/>
+    <row r="861" ht="15.75" customHeight="1" s="31"/>
+    <row r="862" ht="15.75" customHeight="1" s="31"/>
+    <row r="863" ht="15.75" customHeight="1" s="31"/>
+    <row r="864" ht="15.75" customHeight="1" s="31"/>
+    <row r="865" ht="15.75" customHeight="1" s="31"/>
+    <row r="866" ht="15.75" customHeight="1" s="31"/>
+    <row r="867" ht="15.75" customHeight="1" s="31"/>
+    <row r="868" ht="15.75" customHeight="1" s="31"/>
+    <row r="869" ht="15.75" customHeight="1" s="31"/>
+    <row r="870" ht="15.75" customHeight="1" s="31"/>
+    <row r="871" ht="15.75" customHeight="1" s="31"/>
+    <row r="872" ht="15.75" customHeight="1" s="31"/>
+    <row r="873" ht="15.75" customHeight="1" s="31"/>
+    <row r="874" ht="15.75" customHeight="1" s="31"/>
+    <row r="875" ht="15.75" customHeight="1" s="31"/>
+    <row r="876" ht="15.75" customHeight="1" s="31"/>
+    <row r="877" ht="15.75" customHeight="1" s="31"/>
+    <row r="878" ht="15.75" customHeight="1" s="31"/>
+    <row r="879" ht="15.75" customHeight="1" s="31"/>
+    <row r="880" ht="15.75" customHeight="1" s="31"/>
+    <row r="881" ht="15.75" customHeight="1" s="31"/>
+    <row r="882" ht="15.75" customHeight="1" s="31"/>
+    <row r="883" ht="15.75" customHeight="1" s="31"/>
+    <row r="884" ht="15.75" customHeight="1" s="31"/>
+    <row r="885" ht="15.75" customHeight="1" s="31"/>
+    <row r="886" ht="15.75" customHeight="1" s="31"/>
+    <row r="887" ht="15.75" customHeight="1" s="31"/>
+    <row r="888" ht="15.75" customHeight="1" s="31"/>
+    <row r="889" ht="15.75" customHeight="1" s="31"/>
+    <row r="890" ht="15.75" customHeight="1" s="31"/>
+    <row r="891" ht="15.75" customHeight="1" s="31"/>
+    <row r="892" ht="15.75" customHeight="1" s="31"/>
+    <row r="893" ht="15.75" customHeight="1" s="31"/>
+    <row r="894" ht="15.75" customHeight="1" s="31"/>
+    <row r="895" ht="15.75" customHeight="1" s="31"/>
+    <row r="896" ht="15.75" customHeight="1" s="31"/>
+    <row r="897" ht="15.75" customHeight="1" s="31"/>
+    <row r="898" ht="15.75" customHeight="1" s="31"/>
+    <row r="899" ht="15.75" customHeight="1" s="31"/>
+    <row r="900" ht="15.75" customHeight="1" s="31"/>
+    <row r="901" ht="15.75" customHeight="1" s="31"/>
+    <row r="902" ht="15.75" customHeight="1" s="31"/>
+    <row r="903" ht="15.75" customHeight="1" s="31"/>
+    <row r="904" ht="15.75" customHeight="1" s="31"/>
+    <row r="905" ht="15.75" customHeight="1" s="31"/>
+    <row r="906" ht="15.75" customHeight="1" s="31"/>
+    <row r="907" ht="15.75" customHeight="1" s="31"/>
+    <row r="908" ht="15.75" customHeight="1" s="31"/>
+    <row r="909" ht="15.75" customHeight="1" s="31"/>
+    <row r="910" ht="15.75" customHeight="1" s="31"/>
+    <row r="911" ht="15.75" customHeight="1" s="31"/>
+    <row r="912" ht="15.75" customHeight="1" s="31"/>
+    <row r="913" ht="15.75" customHeight="1" s="31"/>
+    <row r="914" ht="15.75" customHeight="1" s="31"/>
+    <row r="915" ht="15.75" customHeight="1" s="31"/>
+    <row r="916" ht="15.75" customHeight="1" s="31"/>
+    <row r="917" ht="15.75" customHeight="1" s="31"/>
+    <row r="918" ht="15.75" customHeight="1" s="31"/>
+    <row r="919" ht="15.75" customHeight="1" s="31"/>
+    <row r="920" ht="15.75" customHeight="1" s="31"/>
+    <row r="921" ht="15.75" customHeight="1" s="31"/>
+    <row r="922" ht="15.75" customHeight="1" s="31"/>
+    <row r="923" ht="15.75" customHeight="1" s="31"/>
+    <row r="924" ht="15.75" customHeight="1" s="31"/>
+    <row r="925" ht="15.75" customHeight="1" s="31"/>
+    <row r="926" ht="15.75" customHeight="1" s="31"/>
+    <row r="927" ht="15.75" customHeight="1" s="31"/>
+    <row r="928" ht="15.75" customHeight="1" s="31"/>
+    <row r="929" ht="15.75" customHeight="1" s="31"/>
+    <row r="930" ht="15.75" customHeight="1" s="31"/>
+    <row r="931" ht="15.75" customHeight="1" s="31"/>
+    <row r="932" ht="15.75" customHeight="1" s="31"/>
+    <row r="933" ht="15.75" customHeight="1" s="31"/>
+    <row r="934" ht="15.75" customHeight="1" s="31"/>
+    <row r="935" ht="15.75" customHeight="1" s="31"/>
+    <row r="936" ht="15.75" customHeight="1" s="31"/>
+    <row r="937" ht="15.75" customHeight="1" s="31"/>
+    <row r="938" ht="15.75" customHeight="1" s="31"/>
+    <row r="939" ht="15.75" customHeight="1" s="31"/>
+    <row r="940" ht="15.75" customHeight="1" s="31"/>
+    <row r="941" ht="15.75" customHeight="1" s="31"/>
+    <row r="942" ht="15.75" customHeight="1" s="31"/>
+    <row r="943" ht="15.75" customHeight="1" s="31"/>
+    <row r="944" ht="15.75" customHeight="1" s="31"/>
+    <row r="945" ht="15.75" customHeight="1" s="31"/>
+    <row r="946" ht="15.75" customHeight="1" s="31"/>
+    <row r="947" ht="15.75" customHeight="1" s="31"/>
+    <row r="948" ht="15.75" customHeight="1" s="31"/>
+    <row r="949" ht="15.75" customHeight="1" s="31"/>
+    <row r="950" ht="15.75" customHeight="1" s="31"/>
+    <row r="951" ht="15.75" customHeight="1" s="31"/>
+    <row r="952" ht="15.75" customHeight="1" s="31"/>
+    <row r="953" ht="15.75" customHeight="1" s="31"/>
+    <row r="954" ht="15.75" customHeight="1" s="31"/>
+    <row r="955" ht="15.75" customHeight="1" s="31"/>
+    <row r="956" ht="15.75" customHeight="1" s="31"/>
+    <row r="957" ht="15.75" customHeight="1" s="31"/>
+    <row r="958" ht="15.75" customHeight="1" s="31"/>
+    <row r="959" ht="15.75" customHeight="1" s="31"/>
+    <row r="960" ht="15.75" customHeight="1" s="31"/>
+    <row r="961" ht="15.75" customHeight="1" s="31"/>
+    <row r="962" ht="15.75" customHeight="1" s="31"/>
+    <row r="963" ht="15.75" customHeight="1" s="31"/>
+    <row r="964" ht="15.75" customHeight="1" s="31"/>
+    <row r="965" ht="15.75" customHeight="1" s="31"/>
+    <row r="966" ht="15.75" customHeight="1" s="31"/>
+    <row r="967" ht="15.75" customHeight="1" s="31"/>
+    <row r="968" ht="15.75" customHeight="1" s="31"/>
+    <row r="969" ht="15.75" customHeight="1" s="31"/>
+    <row r="970" ht="15.75" customHeight="1" s="31"/>
+    <row r="971" ht="15.75" customHeight="1" s="31"/>
+    <row r="972" ht="15.75" customHeight="1" s="31"/>
+    <row r="973" ht="15.75" customHeight="1" s="31"/>
+    <row r="974" ht="15.75" customHeight="1" s="31"/>
+    <row r="975" ht="15.75" customHeight="1" s="31"/>
+    <row r="976" ht="15.75" customHeight="1" s="31"/>
+    <row r="977" ht="15.75" customHeight="1" s="31"/>
+    <row r="978" ht="15.75" customHeight="1" s="31"/>
+    <row r="979" ht="15.75" customHeight="1" s="31"/>
+    <row r="980" ht="15.75" customHeight="1" s="31"/>
+    <row r="981" ht="15.75" customHeight="1" s="31"/>
+    <row r="982" ht="15.75" customHeight="1" s="31"/>
+    <row r="983" ht="15.75" customHeight="1" s="31"/>
+    <row r="984" ht="15.75" customHeight="1" s="31"/>
+    <row r="985" ht="15.75" customHeight="1" s="31"/>
+    <row r="986" ht="15.75" customHeight="1" s="31"/>
+    <row r="987" ht="15.75" customHeight="1" s="31"/>
+    <row r="988" ht="15.75" customHeight="1" s="31"/>
+    <row r="989" ht="15.75" customHeight="1" s="31"/>
+    <row r="990" ht="15.75" customHeight="1" s="31"/>
+    <row r="991" ht="15.75" customHeight="1" s="31"/>
+    <row r="992" ht="15.75" customHeight="1" s="31"/>
+    <row r="993" ht="15.75" customHeight="1" s="31"/>
+    <row r="994" ht="15.75" customHeight="1" s="31"/>
+    <row r="995" ht="15.75" customHeight="1" s="31"/>
+    <row r="996" ht="15.75" customHeight="1" s="31"/>
+    <row r="997" ht="15.75" customHeight="1" s="31"/>
+    <row r="998" ht="15.75" customHeight="1" s="31"/>
+    <row r="999" ht="15.75" customHeight="1" s="31"/>
+    <row r="1000" ht="15.75" customHeight="1" s="31"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="24.75" customWidth="1" style="31" min="1" max="1"/>
+    <col width="56.75" customWidth="1" style="31" min="2" max="2"/>
+    <col width="12.63" customWidth="1" style="31" min="3" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="31">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="31">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.25" customHeight="1" s="31">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>daniel.tan@connectsphere.com is a seeded Coordinator who owns no events of his own. rachel.ng@meridianfina.com owns the seeded draft "Q1 Investor Update (rough idea)". budi.santoso@nusantaratec.com owns the seeded, already-submitted event "Nusantara Developer Summit".</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30.75" customHeight="1" s="31">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Open the "All events" page</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="31">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>N/A — uses seeded data</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="31">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>"Nusantara Developer Summit" appears in the list. "Q1 Investor Update (rough idea)", or any other draft, does not appear anywhere on the page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="31">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="31">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="31"/>
+    <row r="10" ht="15.75" customHeight="1" s="31">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="31">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>"Nusantara Developer Summit" appears in the list. "Q1 Investor Update (rough idea)", or any other draft, does not appear anywhere on the page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="31">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="31">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="31">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="31">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="31"/>
+    <row r="17" ht="15.75" customHeight="1" s="31"/>
+    <row r="18" ht="15.75" customHeight="1" s="31">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="31">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>"Nusantara Developer Summit" appears in the list. "Q1 Investor Update (rough idea)", or any other draft, does not appear anywhere on the page.</t>
         </is>
@@ -13665,6 +14896,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" style="31" min="1" max="1"/>
+    <col width="75" customWidth="1" style="31" min="2" max="2"/>
+    <col width="40" customWidth="1" style="31" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="36" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="36" t="inlineStr">
+        <is>
+          <t>Question / ambiguity for the PO or developer</t>
+        </is>
+      </c>
+      <c r="C1" s="36" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="152.5" customHeight="1" s="31">
+      <c r="A2" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>SPM-24-TC13 originally tested that selecting the same equipment item twice was rejected after the fact, with an error message. The picker was changed so a duplicate can no longer be selected in the first place (the already-chosen item is removed from the other rows' dropdowns), which is why TC13 now tests prevention instead of rejection, and TC13b was added for the 'every item already used' edge case. The server-side Zod rule that used to produce the rejection message is still in place as a safety net (src/lib/validation/events.ts) but is no longer reachable by clicking through the app, so it isn't covered by a manual test case here — only by the existing unit test in src/lib/__tests__/validation.test.ts.</t>
+        </is>
+      </c>
+      <c r="C2" s="37" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -13690,7 +14968,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="35" t="inlineStr">
         <is>
           <t>SPM-24-TC01</t>
         </is>
@@ -13702,7 +14980,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Logged in as Rachel Ng (rachel.ng@meridianfina.com / password123), a seeded Organiser. On the "New event request" page.</t>
         </is>
@@ -13714,7 +14992,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>1. Enter "Annual Partner Appreciation Dinner" into Event name
 2. Leave every other field blank
@@ -13728,7 +15006,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Event name: Annual Partner Appreciation Dinner</t>
         </is>
@@ -13740,7 +15018,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>The browser returns to the "My events" page.
 The event appears under "Drafts — not yet submitted" with the title "Annual Partner Appreciation Dinner" and a "Draft" status badge.</t>
@@ -13753,7 +15031,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -13785,7 +15063,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>The browser returns to the "My events" page.
 The event appears under "Drafts — not yet submitted" with the title "Annual Partner Appreciation Dinner" and a "Draft" status badge.</t>
@@ -13822,7 +15100,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -13899,1231 +15177,6 @@
     </row>
     <row r="23" ht="15.75" customHeight="1" s="31">
       <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="31"/>
-    <row r="25" ht="15.75" customHeight="1" s="31"/>
-    <row r="26" ht="15.75" customHeight="1" s="31"/>
-    <row r="27" ht="15.75" customHeight="1" s="31"/>
-    <row r="28" ht="15.75" customHeight="1" s="31"/>
-    <row r="29" ht="15.75" customHeight="1" s="31"/>
-    <row r="30" ht="15.75" customHeight="1" s="31"/>
-    <row r="31" ht="15.75" customHeight="1" s="31"/>
-    <row r="32" ht="15.75" customHeight="1" s="31"/>
-    <row r="33" ht="15.75" customHeight="1" s="31"/>
-    <row r="34" ht="15.75" customHeight="1" s="31"/>
-    <row r="35" ht="15.75" customHeight="1" s="31"/>
-    <row r="36" ht="15.75" customHeight="1" s="31"/>
-    <row r="37" ht="15.75" customHeight="1" s="31"/>
-    <row r="38" ht="15.75" customHeight="1" s="31"/>
-    <row r="39" ht="15.75" customHeight="1" s="31"/>
-    <row r="40" ht="15.75" customHeight="1" s="31"/>
-    <row r="41" ht="15.75" customHeight="1" s="31"/>
-    <row r="42" ht="15.75" customHeight="1" s="31"/>
-    <row r="43" ht="15.75" customHeight="1" s="31"/>
-    <row r="44" ht="15.75" customHeight="1" s="31"/>
-    <row r="45" ht="15.75" customHeight="1" s="31"/>
-    <row r="46" ht="15.75" customHeight="1" s="31"/>
-    <row r="47" ht="15.75" customHeight="1" s="31"/>
-    <row r="48" ht="15.75" customHeight="1" s="31"/>
-    <row r="49" ht="15.75" customHeight="1" s="31"/>
-    <row r="50" ht="15.75" customHeight="1" s="31"/>
-    <row r="51" ht="15.75" customHeight="1" s="31"/>
-    <row r="52" ht="15.75" customHeight="1" s="31"/>
-    <row r="53" ht="15.75" customHeight="1" s="31"/>
-    <row r="54" ht="15.75" customHeight="1" s="31"/>
-    <row r="55" ht="15.75" customHeight="1" s="31"/>
-    <row r="56" ht="15.75" customHeight="1" s="31"/>
-    <row r="57" ht="15.75" customHeight="1" s="31"/>
-    <row r="58" ht="15.75" customHeight="1" s="31"/>
-    <row r="59" ht="15.75" customHeight="1" s="31"/>
-    <row r="60" ht="15.75" customHeight="1" s="31"/>
-    <row r="61" ht="15.75" customHeight="1" s="31"/>
-    <row r="62" ht="15.75" customHeight="1" s="31"/>
-    <row r="63" ht="15.75" customHeight="1" s="31"/>
-    <row r="64" ht="15.75" customHeight="1" s="31"/>
-    <row r="65" ht="15.75" customHeight="1" s="31"/>
-    <row r="66" ht="15.75" customHeight="1" s="31"/>
-    <row r="67" ht="15.75" customHeight="1" s="31"/>
-    <row r="68" ht="15.75" customHeight="1" s="31"/>
-    <row r="69" ht="15.75" customHeight="1" s="31"/>
-    <row r="70" ht="15.75" customHeight="1" s="31"/>
-    <row r="71" ht="15.75" customHeight="1" s="31"/>
-    <row r="72" ht="15.75" customHeight="1" s="31"/>
-    <row r="73" ht="15.75" customHeight="1" s="31"/>
-    <row r="74" ht="15.75" customHeight="1" s="31"/>
-    <row r="75" ht="15.75" customHeight="1" s="31"/>
-    <row r="76" ht="15.75" customHeight="1" s="31"/>
-    <row r="77" ht="15.75" customHeight="1" s="31"/>
-    <row r="78" ht="15.75" customHeight="1" s="31"/>
-    <row r="79" ht="15.75" customHeight="1" s="31"/>
-    <row r="80" ht="15.75" customHeight="1" s="31"/>
-    <row r="81" ht="15.75" customHeight="1" s="31"/>
-    <row r="82" ht="15.75" customHeight="1" s="31"/>
-    <row r="83" ht="15.75" customHeight="1" s="31"/>
-    <row r="84" ht="15.75" customHeight="1" s="31"/>
-    <row r="85" ht="15.75" customHeight="1" s="31"/>
-    <row r="86" ht="15.75" customHeight="1" s="31"/>
-    <row r="87" ht="15.75" customHeight="1" s="31"/>
-    <row r="88" ht="15.75" customHeight="1" s="31"/>
-    <row r="89" ht="15.75" customHeight="1" s="31"/>
-    <row r="90" ht="15.75" customHeight="1" s="31"/>
-    <row r="91" ht="15.75" customHeight="1" s="31"/>
-    <row r="92" ht="15.75" customHeight="1" s="31"/>
-    <row r="93" ht="15.75" customHeight="1" s="31"/>
-    <row r="94" ht="15.75" customHeight="1" s="31"/>
-    <row r="95" ht="15.75" customHeight="1" s="31"/>
-    <row r="96" ht="15.75" customHeight="1" s="31"/>
-    <row r="97" ht="15.75" customHeight="1" s="31"/>
-    <row r="98" ht="15.75" customHeight="1" s="31"/>
-    <row r="99" ht="15.75" customHeight="1" s="31"/>
-    <row r="100" ht="15.75" customHeight="1" s="31"/>
-    <row r="101" ht="15.75" customHeight="1" s="31"/>
-    <row r="102" ht="15.75" customHeight="1" s="31"/>
-    <row r="103" ht="15.75" customHeight="1" s="31"/>
-    <row r="104" ht="15.75" customHeight="1" s="31"/>
-    <row r="105" ht="15.75" customHeight="1" s="31"/>
-    <row r="106" ht="15.75" customHeight="1" s="31"/>
-    <row r="107" ht="15.75" customHeight="1" s="31"/>
-    <row r="108" ht="15.75" customHeight="1" s="31"/>
-    <row r="109" ht="15.75" customHeight="1" s="31"/>
-    <row r="110" ht="15.75" customHeight="1" s="31"/>
-    <row r="111" ht="15.75" customHeight="1" s="31"/>
-    <row r="112" ht="15.75" customHeight="1" s="31"/>
-    <row r="113" ht="15.75" customHeight="1" s="31"/>
-    <row r="114" ht="15.75" customHeight="1" s="31"/>
-    <row r="115" ht="15.75" customHeight="1" s="31"/>
-    <row r="116" ht="15.75" customHeight="1" s="31"/>
-    <row r="117" ht="15.75" customHeight="1" s="31"/>
-    <row r="118" ht="15.75" customHeight="1" s="31"/>
-    <row r="119" ht="15.75" customHeight="1" s="31"/>
-    <row r="120" ht="15.75" customHeight="1" s="31"/>
-    <row r="121" ht="15.75" customHeight="1" s="31"/>
-    <row r="122" ht="15.75" customHeight="1" s="31"/>
-    <row r="123" ht="15.75" customHeight="1" s="31"/>
-    <row r="124" ht="15.75" customHeight="1" s="31"/>
-    <row r="125" ht="15.75" customHeight="1" s="31"/>
-    <row r="126" ht="15.75" customHeight="1" s="31"/>
-    <row r="127" ht="15.75" customHeight="1" s="31"/>
-    <row r="128" ht="15.75" customHeight="1" s="31"/>
-    <row r="129" ht="15.75" customHeight="1" s="31"/>
-    <row r="130" ht="15.75" customHeight="1" s="31"/>
-    <row r="131" ht="15.75" customHeight="1" s="31"/>
-    <row r="132" ht="15.75" customHeight="1" s="31"/>
-    <row r="133" ht="15.75" customHeight="1" s="31"/>
-    <row r="134" ht="15.75" customHeight="1" s="31"/>
-    <row r="135" ht="15.75" customHeight="1" s="31"/>
-    <row r="136" ht="15.75" customHeight="1" s="31"/>
-    <row r="137" ht="15.75" customHeight="1" s="31"/>
-    <row r="138" ht="15.75" customHeight="1" s="31"/>
-    <row r="139" ht="15.75" customHeight="1" s="31"/>
-    <row r="140" ht="15.75" customHeight="1" s="31"/>
-    <row r="141" ht="15.75" customHeight="1" s="31"/>
-    <row r="142" ht="15.75" customHeight="1" s="31"/>
-    <row r="143" ht="15.75" customHeight="1" s="31"/>
-    <row r="144" ht="15.75" customHeight="1" s="31"/>
-    <row r="145" ht="15.75" customHeight="1" s="31"/>
-    <row r="146" ht="15.75" customHeight="1" s="31"/>
-    <row r="147" ht="15.75" customHeight="1" s="31"/>
-    <row r="148" ht="15.75" customHeight="1" s="31"/>
-    <row r="149" ht="15.75" customHeight="1" s="31"/>
-    <row r="150" ht="15.75" customHeight="1" s="31"/>
-    <row r="151" ht="15.75" customHeight="1" s="31"/>
-    <row r="152" ht="15.75" customHeight="1" s="31"/>
-    <row r="153" ht="15.75" customHeight="1" s="31"/>
-    <row r="154" ht="15.75" customHeight="1" s="31"/>
-    <row r="155" ht="15.75" customHeight="1" s="31"/>
-    <row r="156" ht="15.75" customHeight="1" s="31"/>
-    <row r="157" ht="15.75" customHeight="1" s="31"/>
-    <row r="158" ht="15.75" customHeight="1" s="31"/>
-    <row r="159" ht="15.75" customHeight="1" s="31"/>
-    <row r="160" ht="15.75" customHeight="1" s="31"/>
-    <row r="161" ht="15.75" customHeight="1" s="31"/>
-    <row r="162" ht="15.75" customHeight="1" s="31"/>
-    <row r="163" ht="15.75" customHeight="1" s="31"/>
-    <row r="164" ht="15.75" customHeight="1" s="31"/>
-    <row r="165" ht="15.75" customHeight="1" s="31"/>
-    <row r="166" ht="15.75" customHeight="1" s="31"/>
-    <row r="167" ht="15.75" customHeight="1" s="31"/>
-    <row r="168" ht="15.75" customHeight="1" s="31"/>
-    <row r="169" ht="15.75" customHeight="1" s="31"/>
-    <row r="170" ht="15.75" customHeight="1" s="31"/>
-    <row r="171" ht="15.75" customHeight="1" s="31"/>
-    <row r="172" ht="15.75" customHeight="1" s="31"/>
-    <row r="173" ht="15.75" customHeight="1" s="31"/>
-    <row r="174" ht="15.75" customHeight="1" s="31"/>
-    <row r="175" ht="15.75" customHeight="1" s="31"/>
-    <row r="176" ht="15.75" customHeight="1" s="31"/>
-    <row r="177" ht="15.75" customHeight="1" s="31"/>
-    <row r="178" ht="15.75" customHeight="1" s="31"/>
-    <row r="179" ht="15.75" customHeight="1" s="31"/>
-    <row r="180" ht="15.75" customHeight="1" s="31"/>
-    <row r="181" ht="15.75" customHeight="1" s="31"/>
-    <row r="182" ht="15.75" customHeight="1" s="31"/>
-    <row r="183" ht="15.75" customHeight="1" s="31"/>
-    <row r="184" ht="15.75" customHeight="1" s="31"/>
-    <row r="185" ht="15.75" customHeight="1" s="31"/>
-    <row r="186" ht="15.75" customHeight="1" s="31"/>
-    <row r="187" ht="15.75" customHeight="1" s="31"/>
-    <row r="188" ht="15.75" customHeight="1" s="31"/>
-    <row r="189" ht="15.75" customHeight="1" s="31"/>
-    <row r="190" ht="15.75" customHeight="1" s="31"/>
-    <row r="191" ht="15.75" customHeight="1" s="31"/>
-    <row r="192" ht="15.75" customHeight="1" s="31"/>
-    <row r="193" ht="15.75" customHeight="1" s="31"/>
-    <row r="194" ht="15.75" customHeight="1" s="31"/>
-    <row r="195" ht="15.75" customHeight="1" s="31"/>
-    <row r="196" ht="15.75" customHeight="1" s="31"/>
-    <row r="197" ht="15.75" customHeight="1" s="31"/>
-    <row r="198" ht="15.75" customHeight="1" s="31"/>
-    <row r="199" ht="15.75" customHeight="1" s="31"/>
-    <row r="200" ht="15.75" customHeight="1" s="31"/>
-    <row r="201" ht="15.75" customHeight="1" s="31"/>
-    <row r="202" ht="15.75" customHeight="1" s="31"/>
-    <row r="203" ht="15.75" customHeight="1" s="31"/>
-    <row r="204" ht="15.75" customHeight="1" s="31"/>
-    <row r="205" ht="15.75" customHeight="1" s="31"/>
-    <row r="206" ht="15.75" customHeight="1" s="31"/>
-    <row r="207" ht="15.75" customHeight="1" s="31"/>
-    <row r="208" ht="15.75" customHeight="1" s="31"/>
-    <row r="209" ht="15.75" customHeight="1" s="31"/>
-    <row r="210" ht="15.75" customHeight="1" s="31"/>
-    <row r="211" ht="15.75" customHeight="1" s="31"/>
-    <row r="212" ht="15.75" customHeight="1" s="31"/>
-    <row r="213" ht="15.75" customHeight="1" s="31"/>
-    <row r="214" ht="15.75" customHeight="1" s="31"/>
-    <row r="215" ht="15.75" customHeight="1" s="31"/>
-    <row r="216" ht="15.75" customHeight="1" s="31"/>
-    <row r="217" ht="15.75" customHeight="1" s="31"/>
-    <row r="218" ht="15.75" customHeight="1" s="31"/>
-    <row r="219" ht="15.75" customHeight="1" s="31"/>
-    <row r="220" ht="15.75" customHeight="1" s="31"/>
-    <row r="221" ht="15.75" customHeight="1" s="31"/>
-    <row r="222" ht="15.75" customHeight="1" s="31"/>
-    <row r="223" ht="15.75" customHeight="1" s="31"/>
-    <row r="224" ht="15.75" customHeight="1" s="31"/>
-    <row r="225" ht="15.75" customHeight="1" s="31"/>
-    <row r="226" ht="15.75" customHeight="1" s="31"/>
-    <row r="227" ht="15.75" customHeight="1" s="31"/>
-    <row r="228" ht="15.75" customHeight="1" s="31"/>
-    <row r="229" ht="15.75" customHeight="1" s="31"/>
-    <row r="230" ht="15.75" customHeight="1" s="31"/>
-    <row r="231" ht="15.75" customHeight="1" s="31"/>
-    <row r="232" ht="15.75" customHeight="1" s="31"/>
-    <row r="233" ht="15.75" customHeight="1" s="31"/>
-    <row r="234" ht="15.75" customHeight="1" s="31"/>
-    <row r="235" ht="15.75" customHeight="1" s="31"/>
-    <row r="236" ht="15.75" customHeight="1" s="31"/>
-    <row r="237" ht="15.75" customHeight="1" s="31"/>
-    <row r="238" ht="15.75" customHeight="1" s="31"/>
-    <row r="239" ht="15.75" customHeight="1" s="31"/>
-    <row r="240" ht="15.75" customHeight="1" s="31"/>
-    <row r="241" ht="15.75" customHeight="1" s="31"/>
-    <row r="242" ht="15.75" customHeight="1" s="31"/>
-    <row r="243" ht="15.75" customHeight="1" s="31"/>
-    <row r="244" ht="15.75" customHeight="1" s="31"/>
-    <row r="245" ht="15.75" customHeight="1" s="31"/>
-    <row r="246" ht="15.75" customHeight="1" s="31"/>
-    <row r="247" ht="15.75" customHeight="1" s="31"/>
-    <row r="248" ht="15.75" customHeight="1" s="31"/>
-    <row r="249" ht="15.75" customHeight="1" s="31"/>
-    <row r="250" ht="15.75" customHeight="1" s="31"/>
-    <row r="251" ht="15.75" customHeight="1" s="31"/>
-    <row r="252" ht="15.75" customHeight="1" s="31"/>
-    <row r="253" ht="15.75" customHeight="1" s="31"/>
-    <row r="254" ht="15.75" customHeight="1" s="31"/>
-    <row r="255" ht="15.75" customHeight="1" s="31"/>
-    <row r="256" ht="15.75" customHeight="1" s="31"/>
-    <row r="257" ht="15.75" customHeight="1" s="31"/>
-    <row r="258" ht="15.75" customHeight="1" s="31"/>
-    <row r="259" ht="15.75" customHeight="1" s="31"/>
-    <row r="260" ht="15.75" customHeight="1" s="31"/>
-    <row r="261" ht="15.75" customHeight="1" s="31"/>
-    <row r="262" ht="15.75" customHeight="1" s="31"/>
-    <row r="263" ht="15.75" customHeight="1" s="31"/>
-    <row r="264" ht="15.75" customHeight="1" s="31"/>
-    <row r="265" ht="15.75" customHeight="1" s="31"/>
-    <row r="266" ht="15.75" customHeight="1" s="31"/>
-    <row r="267" ht="15.75" customHeight="1" s="31"/>
-    <row r="268" ht="15.75" customHeight="1" s="31"/>
-    <row r="269" ht="15.75" customHeight="1" s="31"/>
-    <row r="270" ht="15.75" customHeight="1" s="31"/>
-    <row r="271" ht="15.75" customHeight="1" s="31"/>
-    <row r="272" ht="15.75" customHeight="1" s="31"/>
-    <row r="273" ht="15.75" customHeight="1" s="31"/>
-    <row r="274" ht="15.75" customHeight="1" s="31"/>
-    <row r="275" ht="15.75" customHeight="1" s="31"/>
-    <row r="276" ht="15.75" customHeight="1" s="31"/>
-    <row r="277" ht="15.75" customHeight="1" s="31"/>
-    <row r="278" ht="15.75" customHeight="1" s="31"/>
-    <row r="279" ht="15.75" customHeight="1" s="31"/>
-    <row r="280" ht="15.75" customHeight="1" s="31"/>
-    <row r="281" ht="15.75" customHeight="1" s="31"/>
-    <row r="282" ht="15.75" customHeight="1" s="31"/>
-    <row r="283" ht="15.75" customHeight="1" s="31"/>
-    <row r="284" ht="15.75" customHeight="1" s="31"/>
-    <row r="285" ht="15.75" customHeight="1" s="31"/>
-    <row r="286" ht="15.75" customHeight="1" s="31"/>
-    <row r="287" ht="15.75" customHeight="1" s="31"/>
-    <row r="288" ht="15.75" customHeight="1" s="31"/>
-    <row r="289" ht="15.75" customHeight="1" s="31"/>
-    <row r="290" ht="15.75" customHeight="1" s="31"/>
-    <row r="291" ht="15.75" customHeight="1" s="31"/>
-    <row r="292" ht="15.75" customHeight="1" s="31"/>
-    <row r="293" ht="15.75" customHeight="1" s="31"/>
-    <row r="294" ht="15.75" customHeight="1" s="31"/>
-    <row r="295" ht="15.75" customHeight="1" s="31"/>
-    <row r="296" ht="15.75" customHeight="1" s="31"/>
-    <row r="297" ht="15.75" customHeight="1" s="31"/>
-    <row r="298" ht="15.75" customHeight="1" s="31"/>
-    <row r="299" ht="15.75" customHeight="1" s="31"/>
-    <row r="300" ht="15.75" customHeight="1" s="31"/>
-    <row r="301" ht="15.75" customHeight="1" s="31"/>
-    <row r="302" ht="15.75" customHeight="1" s="31"/>
-    <row r="303" ht="15.75" customHeight="1" s="31"/>
-    <row r="304" ht="15.75" customHeight="1" s="31"/>
-    <row r="305" ht="15.75" customHeight="1" s="31"/>
-    <row r="306" ht="15.75" customHeight="1" s="31"/>
-    <row r="307" ht="15.75" customHeight="1" s="31"/>
-    <row r="308" ht="15.75" customHeight="1" s="31"/>
-    <row r="309" ht="15.75" customHeight="1" s="31"/>
-    <row r="310" ht="15.75" customHeight="1" s="31"/>
-    <row r="311" ht="15.75" customHeight="1" s="31"/>
-    <row r="312" ht="15.75" customHeight="1" s="31"/>
-    <row r="313" ht="15.75" customHeight="1" s="31"/>
-    <row r="314" ht="15.75" customHeight="1" s="31"/>
-    <row r="315" ht="15.75" customHeight="1" s="31"/>
-    <row r="316" ht="15.75" customHeight="1" s="31"/>
-    <row r="317" ht="15.75" customHeight="1" s="31"/>
-    <row r="318" ht="15.75" customHeight="1" s="31"/>
-    <row r="319" ht="15.75" customHeight="1" s="31"/>
-    <row r="320" ht="15.75" customHeight="1" s="31"/>
-    <row r="321" ht="15.75" customHeight="1" s="31"/>
-    <row r="322" ht="15.75" customHeight="1" s="31"/>
-    <row r="323" ht="15.75" customHeight="1" s="31"/>
-    <row r="324" ht="15.75" customHeight="1" s="31"/>
-    <row r="325" ht="15.75" customHeight="1" s="31"/>
-    <row r="326" ht="15.75" customHeight="1" s="31"/>
-    <row r="327" ht="15.75" customHeight="1" s="31"/>
-    <row r="328" ht="15.75" customHeight="1" s="31"/>
-    <row r="329" ht="15.75" customHeight="1" s="31"/>
-    <row r="330" ht="15.75" customHeight="1" s="31"/>
-    <row r="331" ht="15.75" customHeight="1" s="31"/>
-    <row r="332" ht="15.75" customHeight="1" s="31"/>
-    <row r="333" ht="15.75" customHeight="1" s="31"/>
-    <row r="334" ht="15.75" customHeight="1" s="31"/>
-    <row r="335" ht="15.75" customHeight="1" s="31"/>
-    <row r="336" ht="15.75" customHeight="1" s="31"/>
-    <row r="337" ht="15.75" customHeight="1" s="31"/>
-    <row r="338" ht="15.75" customHeight="1" s="31"/>
-    <row r="339" ht="15.75" customHeight="1" s="31"/>
-    <row r="340" ht="15.75" customHeight="1" s="31"/>
-    <row r="341" ht="15.75" customHeight="1" s="31"/>
-    <row r="342" ht="15.75" customHeight="1" s="31"/>
-    <row r="343" ht="15.75" customHeight="1" s="31"/>
-    <row r="344" ht="15.75" customHeight="1" s="31"/>
-    <row r="345" ht="15.75" customHeight="1" s="31"/>
-    <row r="346" ht="15.75" customHeight="1" s="31"/>
-    <row r="347" ht="15.75" customHeight="1" s="31"/>
-    <row r="348" ht="15.75" customHeight="1" s="31"/>
-    <row r="349" ht="15.75" customHeight="1" s="31"/>
-    <row r="350" ht="15.75" customHeight="1" s="31"/>
-    <row r="351" ht="15.75" customHeight="1" s="31"/>
-    <row r="352" ht="15.75" customHeight="1" s="31"/>
-    <row r="353" ht="15.75" customHeight="1" s="31"/>
-    <row r="354" ht="15.75" customHeight="1" s="31"/>
-    <row r="355" ht="15.75" customHeight="1" s="31"/>
-    <row r="356" ht="15.75" customHeight="1" s="31"/>
-    <row r="357" ht="15.75" customHeight="1" s="31"/>
-    <row r="358" ht="15.75" customHeight="1" s="31"/>
-    <row r="359" ht="15.75" customHeight="1" s="31"/>
-    <row r="360" ht="15.75" customHeight="1" s="31"/>
-    <row r="361" ht="15.75" customHeight="1" s="31"/>
-    <row r="362" ht="15.75" customHeight="1" s="31"/>
-    <row r="363" ht="15.75" customHeight="1" s="31"/>
-    <row r="364" ht="15.75" customHeight="1" s="31"/>
-    <row r="365" ht="15.75" customHeight="1" s="31"/>
-    <row r="366" ht="15.75" customHeight="1" s="31"/>
-    <row r="367" ht="15.75" customHeight="1" s="31"/>
-    <row r="368" ht="15.75" customHeight="1" s="31"/>
-    <row r="369" ht="15.75" customHeight="1" s="31"/>
-    <row r="370" ht="15.75" customHeight="1" s="31"/>
-    <row r="371" ht="15.75" customHeight="1" s="31"/>
-    <row r="372" ht="15.75" customHeight="1" s="31"/>
-    <row r="373" ht="15.75" customHeight="1" s="31"/>
-    <row r="374" ht="15.75" customHeight="1" s="31"/>
-    <row r="375" ht="15.75" customHeight="1" s="31"/>
-    <row r="376" ht="15.75" customHeight="1" s="31"/>
-    <row r="377" ht="15.75" customHeight="1" s="31"/>
-    <row r="378" ht="15.75" customHeight="1" s="31"/>
-    <row r="379" ht="15.75" customHeight="1" s="31"/>
-    <row r="380" ht="15.75" customHeight="1" s="31"/>
-    <row r="381" ht="15.75" customHeight="1" s="31"/>
-    <row r="382" ht="15.75" customHeight="1" s="31"/>
-    <row r="383" ht="15.75" customHeight="1" s="31"/>
-    <row r="384" ht="15.75" customHeight="1" s="31"/>
-    <row r="385" ht="15.75" customHeight="1" s="31"/>
-    <row r="386" ht="15.75" customHeight="1" s="31"/>
-    <row r="387" ht="15.75" customHeight="1" s="31"/>
-    <row r="388" ht="15.75" customHeight="1" s="31"/>
-    <row r="389" ht="15.75" customHeight="1" s="31"/>
-    <row r="390" ht="15.75" customHeight="1" s="31"/>
-    <row r="391" ht="15.75" customHeight="1" s="31"/>
-    <row r="392" ht="15.75" customHeight="1" s="31"/>
-    <row r="393" ht="15.75" customHeight="1" s="31"/>
-    <row r="394" ht="15.75" customHeight="1" s="31"/>
-    <row r="395" ht="15.75" customHeight="1" s="31"/>
-    <row r="396" ht="15.75" customHeight="1" s="31"/>
-    <row r="397" ht="15.75" customHeight="1" s="31"/>
-    <row r="398" ht="15.75" customHeight="1" s="31"/>
-    <row r="399" ht="15.75" customHeight="1" s="31"/>
-    <row r="400" ht="15.75" customHeight="1" s="31"/>
-    <row r="401" ht="15.75" customHeight="1" s="31"/>
-    <row r="402" ht="15.75" customHeight="1" s="31"/>
-    <row r="403" ht="15.75" customHeight="1" s="31"/>
-    <row r="404" ht="15.75" customHeight="1" s="31"/>
-    <row r="405" ht="15.75" customHeight="1" s="31"/>
-    <row r="406" ht="15.75" customHeight="1" s="31"/>
-    <row r="407" ht="15.75" customHeight="1" s="31"/>
-    <row r="408" ht="15.75" customHeight="1" s="31"/>
-    <row r="409" ht="15.75" customHeight="1" s="31"/>
-    <row r="410" ht="15.75" customHeight="1" s="31"/>
-    <row r="411" ht="15.75" customHeight="1" s="31"/>
-    <row r="412" ht="15.75" customHeight="1" s="31"/>
-    <row r="413" ht="15.75" customHeight="1" s="31"/>
-    <row r="414" ht="15.75" customHeight="1" s="31"/>
-    <row r="415" ht="15.75" customHeight="1" s="31"/>
-    <row r="416" ht="15.75" customHeight="1" s="31"/>
-    <row r="417" ht="15.75" customHeight="1" s="31"/>
-    <row r="418" ht="15.75" customHeight="1" s="31"/>
-    <row r="419" ht="15.75" customHeight="1" s="31"/>
-    <row r="420" ht="15.75" customHeight="1" s="31"/>
-    <row r="421" ht="15.75" customHeight="1" s="31"/>
-    <row r="422" ht="15.75" customHeight="1" s="31"/>
-    <row r="423" ht="15.75" customHeight="1" s="31"/>
-    <row r="424" ht="15.75" customHeight="1" s="31"/>
-    <row r="425" ht="15.75" customHeight="1" s="31"/>
-    <row r="426" ht="15.75" customHeight="1" s="31"/>
-    <row r="427" ht="15.75" customHeight="1" s="31"/>
-    <row r="428" ht="15.75" customHeight="1" s="31"/>
-    <row r="429" ht="15.75" customHeight="1" s="31"/>
-    <row r="430" ht="15.75" customHeight="1" s="31"/>
-    <row r="431" ht="15.75" customHeight="1" s="31"/>
-    <row r="432" ht="15.75" customHeight="1" s="31"/>
-    <row r="433" ht="15.75" customHeight="1" s="31"/>
-    <row r="434" ht="15.75" customHeight="1" s="31"/>
-    <row r="435" ht="15.75" customHeight="1" s="31"/>
-    <row r="436" ht="15.75" customHeight="1" s="31"/>
-    <row r="437" ht="15.75" customHeight="1" s="31"/>
-    <row r="438" ht="15.75" customHeight="1" s="31"/>
-    <row r="439" ht="15.75" customHeight="1" s="31"/>
-    <row r="440" ht="15.75" customHeight="1" s="31"/>
-    <row r="441" ht="15.75" customHeight="1" s="31"/>
-    <row r="442" ht="15.75" customHeight="1" s="31"/>
-    <row r="443" ht="15.75" customHeight="1" s="31"/>
-    <row r="444" ht="15.75" customHeight="1" s="31"/>
-    <row r="445" ht="15.75" customHeight="1" s="31"/>
-    <row r="446" ht="15.75" customHeight="1" s="31"/>
-    <row r="447" ht="15.75" customHeight="1" s="31"/>
-    <row r="448" ht="15.75" customHeight="1" s="31"/>
-    <row r="449" ht="15.75" customHeight="1" s="31"/>
-    <row r="450" ht="15.75" customHeight="1" s="31"/>
-    <row r="451" ht="15.75" customHeight="1" s="31"/>
-    <row r="452" ht="15.75" customHeight="1" s="31"/>
-    <row r="453" ht="15.75" customHeight="1" s="31"/>
-    <row r="454" ht="15.75" customHeight="1" s="31"/>
-    <row r="455" ht="15.75" customHeight="1" s="31"/>
-    <row r="456" ht="15.75" customHeight="1" s="31"/>
-    <row r="457" ht="15.75" customHeight="1" s="31"/>
-    <row r="458" ht="15.75" customHeight="1" s="31"/>
-    <row r="459" ht="15.75" customHeight="1" s="31"/>
-    <row r="460" ht="15.75" customHeight="1" s="31"/>
-    <row r="461" ht="15.75" customHeight="1" s="31"/>
-    <row r="462" ht="15.75" customHeight="1" s="31"/>
-    <row r="463" ht="15.75" customHeight="1" s="31"/>
-    <row r="464" ht="15.75" customHeight="1" s="31"/>
-    <row r="465" ht="15.75" customHeight="1" s="31"/>
-    <row r="466" ht="15.75" customHeight="1" s="31"/>
-    <row r="467" ht="15.75" customHeight="1" s="31"/>
-    <row r="468" ht="15.75" customHeight="1" s="31"/>
-    <row r="469" ht="15.75" customHeight="1" s="31"/>
-    <row r="470" ht="15.75" customHeight="1" s="31"/>
-    <row r="471" ht="15.75" customHeight="1" s="31"/>
-    <row r="472" ht="15.75" customHeight="1" s="31"/>
-    <row r="473" ht="15.75" customHeight="1" s="31"/>
-    <row r="474" ht="15.75" customHeight="1" s="31"/>
-    <row r="475" ht="15.75" customHeight="1" s="31"/>
-    <row r="476" ht="15.75" customHeight="1" s="31"/>
-    <row r="477" ht="15.75" customHeight="1" s="31"/>
-    <row r="478" ht="15.75" customHeight="1" s="31"/>
-    <row r="479" ht="15.75" customHeight="1" s="31"/>
-    <row r="480" ht="15.75" customHeight="1" s="31"/>
-    <row r="481" ht="15.75" customHeight="1" s="31"/>
-    <row r="482" ht="15.75" customHeight="1" s="31"/>
-    <row r="483" ht="15.75" customHeight="1" s="31"/>
-    <row r="484" ht="15.75" customHeight="1" s="31"/>
-    <row r="485" ht="15.75" customHeight="1" s="31"/>
-    <row r="486" ht="15.75" customHeight="1" s="31"/>
-    <row r="487" ht="15.75" customHeight="1" s="31"/>
-    <row r="488" ht="15.75" customHeight="1" s="31"/>
-    <row r="489" ht="15.75" customHeight="1" s="31"/>
-    <row r="490" ht="15.75" customHeight="1" s="31"/>
-    <row r="491" ht="15.75" customHeight="1" s="31"/>
-    <row r="492" ht="15.75" customHeight="1" s="31"/>
-    <row r="493" ht="15.75" customHeight="1" s="31"/>
-    <row r="494" ht="15.75" customHeight="1" s="31"/>
-    <row r="495" ht="15.75" customHeight="1" s="31"/>
-    <row r="496" ht="15.75" customHeight="1" s="31"/>
-    <row r="497" ht="15.75" customHeight="1" s="31"/>
-    <row r="498" ht="15.75" customHeight="1" s="31"/>
-    <row r="499" ht="15.75" customHeight="1" s="31"/>
-    <row r="500" ht="15.75" customHeight="1" s="31"/>
-    <row r="501" ht="15.75" customHeight="1" s="31"/>
-    <row r="502" ht="15.75" customHeight="1" s="31"/>
-    <row r="503" ht="15.75" customHeight="1" s="31"/>
-    <row r="504" ht="15.75" customHeight="1" s="31"/>
-    <row r="505" ht="15.75" customHeight="1" s="31"/>
-    <row r="506" ht="15.75" customHeight="1" s="31"/>
-    <row r="507" ht="15.75" customHeight="1" s="31"/>
-    <row r="508" ht="15.75" customHeight="1" s="31"/>
-    <row r="509" ht="15.75" customHeight="1" s="31"/>
-    <row r="510" ht="15.75" customHeight="1" s="31"/>
-    <row r="511" ht="15.75" customHeight="1" s="31"/>
-    <row r="512" ht="15.75" customHeight="1" s="31"/>
-    <row r="513" ht="15.75" customHeight="1" s="31"/>
-    <row r="514" ht="15.75" customHeight="1" s="31"/>
-    <row r="515" ht="15.75" customHeight="1" s="31"/>
-    <row r="516" ht="15.75" customHeight="1" s="31"/>
-    <row r="517" ht="15.75" customHeight="1" s="31"/>
-    <row r="518" ht="15.75" customHeight="1" s="31"/>
-    <row r="519" ht="15.75" customHeight="1" s="31"/>
-    <row r="520" ht="15.75" customHeight="1" s="31"/>
-    <row r="521" ht="15.75" customHeight="1" s="31"/>
-    <row r="522" ht="15.75" customHeight="1" s="31"/>
-    <row r="523" ht="15.75" customHeight="1" s="31"/>
-    <row r="524" ht="15.75" customHeight="1" s="31"/>
-    <row r="525" ht="15.75" customHeight="1" s="31"/>
-    <row r="526" ht="15.75" customHeight="1" s="31"/>
-    <row r="527" ht="15.75" customHeight="1" s="31"/>
-    <row r="528" ht="15.75" customHeight="1" s="31"/>
-    <row r="529" ht="15.75" customHeight="1" s="31"/>
-    <row r="530" ht="15.75" customHeight="1" s="31"/>
-    <row r="531" ht="15.75" customHeight="1" s="31"/>
-    <row r="532" ht="15.75" customHeight="1" s="31"/>
-    <row r="533" ht="15.75" customHeight="1" s="31"/>
-    <row r="534" ht="15.75" customHeight="1" s="31"/>
-    <row r="535" ht="15.75" customHeight="1" s="31"/>
-    <row r="536" ht="15.75" customHeight="1" s="31"/>
-    <row r="537" ht="15.75" customHeight="1" s="31"/>
-    <row r="538" ht="15.75" customHeight="1" s="31"/>
-    <row r="539" ht="15.75" customHeight="1" s="31"/>
-    <row r="540" ht="15.75" customHeight="1" s="31"/>
-    <row r="541" ht="15.75" customHeight="1" s="31"/>
-    <row r="542" ht="15.75" customHeight="1" s="31"/>
-    <row r="543" ht="15.75" customHeight="1" s="31"/>
-    <row r="544" ht="15.75" customHeight="1" s="31"/>
-    <row r="545" ht="15.75" customHeight="1" s="31"/>
-    <row r="546" ht="15.75" customHeight="1" s="31"/>
-    <row r="547" ht="15.75" customHeight="1" s="31"/>
-    <row r="548" ht="15.75" customHeight="1" s="31"/>
-    <row r="549" ht="15.75" customHeight="1" s="31"/>
-    <row r="550" ht="15.75" customHeight="1" s="31"/>
-    <row r="551" ht="15.75" customHeight="1" s="31"/>
-    <row r="552" ht="15.75" customHeight="1" s="31"/>
-    <row r="553" ht="15.75" customHeight="1" s="31"/>
-    <row r="554" ht="15.75" customHeight="1" s="31"/>
-    <row r="555" ht="15.75" customHeight="1" s="31"/>
-    <row r="556" ht="15.75" customHeight="1" s="31"/>
-    <row r="557" ht="15.75" customHeight="1" s="31"/>
-    <row r="558" ht="15.75" customHeight="1" s="31"/>
-    <row r="559" ht="15.75" customHeight="1" s="31"/>
-    <row r="560" ht="15.75" customHeight="1" s="31"/>
-    <row r="561" ht="15.75" customHeight="1" s="31"/>
-    <row r="562" ht="15.75" customHeight="1" s="31"/>
-    <row r="563" ht="15.75" customHeight="1" s="31"/>
-    <row r="564" ht="15.75" customHeight="1" s="31"/>
-    <row r="565" ht="15.75" customHeight="1" s="31"/>
-    <row r="566" ht="15.75" customHeight="1" s="31"/>
-    <row r="567" ht="15.75" customHeight="1" s="31"/>
-    <row r="568" ht="15.75" customHeight="1" s="31"/>
-    <row r="569" ht="15.75" customHeight="1" s="31"/>
-    <row r="570" ht="15.75" customHeight="1" s="31"/>
-    <row r="571" ht="15.75" customHeight="1" s="31"/>
-    <row r="572" ht="15.75" customHeight="1" s="31"/>
-    <row r="573" ht="15.75" customHeight="1" s="31"/>
-    <row r="574" ht="15.75" customHeight="1" s="31"/>
-    <row r="575" ht="15.75" customHeight="1" s="31"/>
-    <row r="576" ht="15.75" customHeight="1" s="31"/>
-    <row r="577" ht="15.75" customHeight="1" s="31"/>
-    <row r="578" ht="15.75" customHeight="1" s="31"/>
-    <row r="579" ht="15.75" customHeight="1" s="31"/>
-    <row r="580" ht="15.75" customHeight="1" s="31"/>
-    <row r="581" ht="15.75" customHeight="1" s="31"/>
-    <row r="582" ht="15.75" customHeight="1" s="31"/>
-    <row r="583" ht="15.75" customHeight="1" s="31"/>
-    <row r="584" ht="15.75" customHeight="1" s="31"/>
-    <row r="585" ht="15.75" customHeight="1" s="31"/>
-    <row r="586" ht="15.75" customHeight="1" s="31"/>
-    <row r="587" ht="15.75" customHeight="1" s="31"/>
-    <row r="588" ht="15.75" customHeight="1" s="31"/>
-    <row r="589" ht="15.75" customHeight="1" s="31"/>
-    <row r="590" ht="15.75" customHeight="1" s="31"/>
-    <row r="591" ht="15.75" customHeight="1" s="31"/>
-    <row r="592" ht="15.75" customHeight="1" s="31"/>
-    <row r="593" ht="15.75" customHeight="1" s="31"/>
-    <row r="594" ht="15.75" customHeight="1" s="31"/>
-    <row r="595" ht="15.75" customHeight="1" s="31"/>
-    <row r="596" ht="15.75" customHeight="1" s="31"/>
-    <row r="597" ht="15.75" customHeight="1" s="31"/>
-    <row r="598" ht="15.75" customHeight="1" s="31"/>
-    <row r="599" ht="15.75" customHeight="1" s="31"/>
-    <row r="600" ht="15.75" customHeight="1" s="31"/>
-    <row r="601" ht="15.75" customHeight="1" s="31"/>
-    <row r="602" ht="15.75" customHeight="1" s="31"/>
-    <row r="603" ht="15.75" customHeight="1" s="31"/>
-    <row r="604" ht="15.75" customHeight="1" s="31"/>
-    <row r="605" ht="15.75" customHeight="1" s="31"/>
-    <row r="606" ht="15.75" customHeight="1" s="31"/>
-    <row r="607" ht="15.75" customHeight="1" s="31"/>
-    <row r="608" ht="15.75" customHeight="1" s="31"/>
-    <row r="609" ht="15.75" customHeight="1" s="31"/>
-    <row r="610" ht="15.75" customHeight="1" s="31"/>
-    <row r="611" ht="15.75" customHeight="1" s="31"/>
-    <row r="612" ht="15.75" customHeight="1" s="31"/>
-    <row r="613" ht="15.75" customHeight="1" s="31"/>
-    <row r="614" ht="15.75" customHeight="1" s="31"/>
-    <row r="615" ht="15.75" customHeight="1" s="31"/>
-    <row r="616" ht="15.75" customHeight="1" s="31"/>
-    <row r="617" ht="15.75" customHeight="1" s="31"/>
-    <row r="618" ht="15.75" customHeight="1" s="31"/>
-    <row r="619" ht="15.75" customHeight="1" s="31"/>
-    <row r="620" ht="15.75" customHeight="1" s="31"/>
-    <row r="621" ht="15.75" customHeight="1" s="31"/>
-    <row r="622" ht="15.75" customHeight="1" s="31"/>
-    <row r="623" ht="15.75" customHeight="1" s="31"/>
-    <row r="624" ht="15.75" customHeight="1" s="31"/>
-    <row r="625" ht="15.75" customHeight="1" s="31"/>
-    <row r="626" ht="15.75" customHeight="1" s="31"/>
-    <row r="627" ht="15.75" customHeight="1" s="31"/>
-    <row r="628" ht="15.75" customHeight="1" s="31"/>
-    <row r="629" ht="15.75" customHeight="1" s="31"/>
-    <row r="630" ht="15.75" customHeight="1" s="31"/>
-    <row r="631" ht="15.75" customHeight="1" s="31"/>
-    <row r="632" ht="15.75" customHeight="1" s="31"/>
-    <row r="633" ht="15.75" customHeight="1" s="31"/>
-    <row r="634" ht="15.75" customHeight="1" s="31"/>
-    <row r="635" ht="15.75" customHeight="1" s="31"/>
-    <row r="636" ht="15.75" customHeight="1" s="31"/>
-    <row r="637" ht="15.75" customHeight="1" s="31"/>
-    <row r="638" ht="15.75" customHeight="1" s="31"/>
-    <row r="639" ht="15.75" customHeight="1" s="31"/>
-    <row r="640" ht="15.75" customHeight="1" s="31"/>
-    <row r="641" ht="15.75" customHeight="1" s="31"/>
-    <row r="642" ht="15.75" customHeight="1" s="31"/>
-    <row r="643" ht="15.75" customHeight="1" s="31"/>
-    <row r="644" ht="15.75" customHeight="1" s="31"/>
-    <row r="645" ht="15.75" customHeight="1" s="31"/>
-    <row r="646" ht="15.75" customHeight="1" s="31"/>
-    <row r="647" ht="15.75" customHeight="1" s="31"/>
-    <row r="648" ht="15.75" customHeight="1" s="31"/>
-    <row r="649" ht="15.75" customHeight="1" s="31"/>
-    <row r="650" ht="15.75" customHeight="1" s="31"/>
-    <row r="651" ht="15.75" customHeight="1" s="31"/>
-    <row r="652" ht="15.75" customHeight="1" s="31"/>
-    <row r="653" ht="15.75" customHeight="1" s="31"/>
-    <row r="654" ht="15.75" customHeight="1" s="31"/>
-    <row r="655" ht="15.75" customHeight="1" s="31"/>
-    <row r="656" ht="15.75" customHeight="1" s="31"/>
-    <row r="657" ht="15.75" customHeight="1" s="31"/>
-    <row r="658" ht="15.75" customHeight="1" s="31"/>
-    <row r="659" ht="15.75" customHeight="1" s="31"/>
-    <row r="660" ht="15.75" customHeight="1" s="31"/>
-    <row r="661" ht="15.75" customHeight="1" s="31"/>
-    <row r="662" ht="15.75" customHeight="1" s="31"/>
-    <row r="663" ht="15.75" customHeight="1" s="31"/>
-    <row r="664" ht="15.75" customHeight="1" s="31"/>
-    <row r="665" ht="15.75" customHeight="1" s="31"/>
-    <row r="666" ht="15.75" customHeight="1" s="31"/>
-    <row r="667" ht="15.75" customHeight="1" s="31"/>
-    <row r="668" ht="15.75" customHeight="1" s="31"/>
-    <row r="669" ht="15.75" customHeight="1" s="31"/>
-    <row r="670" ht="15.75" customHeight="1" s="31"/>
-    <row r="671" ht="15.75" customHeight="1" s="31"/>
-    <row r="672" ht="15.75" customHeight="1" s="31"/>
-    <row r="673" ht="15.75" customHeight="1" s="31"/>
-    <row r="674" ht="15.75" customHeight="1" s="31"/>
-    <row r="675" ht="15.75" customHeight="1" s="31"/>
-    <row r="676" ht="15.75" customHeight="1" s="31"/>
-    <row r="677" ht="15.75" customHeight="1" s="31"/>
-    <row r="678" ht="15.75" customHeight="1" s="31"/>
-    <row r="679" ht="15.75" customHeight="1" s="31"/>
-    <row r="680" ht="15.75" customHeight="1" s="31"/>
-    <row r="681" ht="15.75" customHeight="1" s="31"/>
-    <row r="682" ht="15.75" customHeight="1" s="31"/>
-    <row r="683" ht="15.75" customHeight="1" s="31"/>
-    <row r="684" ht="15.75" customHeight="1" s="31"/>
-    <row r="685" ht="15.75" customHeight="1" s="31"/>
-    <row r="686" ht="15.75" customHeight="1" s="31"/>
-    <row r="687" ht="15.75" customHeight="1" s="31"/>
-    <row r="688" ht="15.75" customHeight="1" s="31"/>
-    <row r="689" ht="15.75" customHeight="1" s="31"/>
-    <row r="690" ht="15.75" customHeight="1" s="31"/>
-    <row r="691" ht="15.75" customHeight="1" s="31"/>
-    <row r="692" ht="15.75" customHeight="1" s="31"/>
-    <row r="693" ht="15.75" customHeight="1" s="31"/>
-    <row r="694" ht="15.75" customHeight="1" s="31"/>
-    <row r="695" ht="15.75" customHeight="1" s="31"/>
-    <row r="696" ht="15.75" customHeight="1" s="31"/>
-    <row r="697" ht="15.75" customHeight="1" s="31"/>
-    <row r="698" ht="15.75" customHeight="1" s="31"/>
-    <row r="699" ht="15.75" customHeight="1" s="31"/>
-    <row r="700" ht="15.75" customHeight="1" s="31"/>
-    <row r="701" ht="15.75" customHeight="1" s="31"/>
-    <row r="702" ht="15.75" customHeight="1" s="31"/>
-    <row r="703" ht="15.75" customHeight="1" s="31"/>
-    <row r="704" ht="15.75" customHeight="1" s="31"/>
-    <row r="705" ht="15.75" customHeight="1" s="31"/>
-    <row r="706" ht="15.75" customHeight="1" s="31"/>
-    <row r="707" ht="15.75" customHeight="1" s="31"/>
-    <row r="708" ht="15.75" customHeight="1" s="31"/>
-    <row r="709" ht="15.75" customHeight="1" s="31"/>
-    <row r="710" ht="15.75" customHeight="1" s="31"/>
-    <row r="711" ht="15.75" customHeight="1" s="31"/>
-    <row r="712" ht="15.75" customHeight="1" s="31"/>
-    <row r="713" ht="15.75" customHeight="1" s="31"/>
-    <row r="714" ht="15.75" customHeight="1" s="31"/>
-    <row r="715" ht="15.75" customHeight="1" s="31"/>
-    <row r="716" ht="15.75" customHeight="1" s="31"/>
-    <row r="717" ht="15.75" customHeight="1" s="31"/>
-    <row r="718" ht="15.75" customHeight="1" s="31"/>
-    <row r="719" ht="15.75" customHeight="1" s="31"/>
-    <row r="720" ht="15.75" customHeight="1" s="31"/>
-    <row r="721" ht="15.75" customHeight="1" s="31"/>
-    <row r="722" ht="15.75" customHeight="1" s="31"/>
-    <row r="723" ht="15.75" customHeight="1" s="31"/>
-    <row r="724" ht="15.75" customHeight="1" s="31"/>
-    <row r="725" ht="15.75" customHeight="1" s="31"/>
-    <row r="726" ht="15.75" customHeight="1" s="31"/>
-    <row r="727" ht="15.75" customHeight="1" s="31"/>
-    <row r="728" ht="15.75" customHeight="1" s="31"/>
-    <row r="729" ht="15.75" customHeight="1" s="31"/>
-    <row r="730" ht="15.75" customHeight="1" s="31"/>
-    <row r="731" ht="15.75" customHeight="1" s="31"/>
-    <row r="732" ht="15.75" customHeight="1" s="31"/>
-    <row r="733" ht="15.75" customHeight="1" s="31"/>
-    <row r="734" ht="15.75" customHeight="1" s="31"/>
-    <row r="735" ht="15.75" customHeight="1" s="31"/>
-    <row r="736" ht="15.75" customHeight="1" s="31"/>
-    <row r="737" ht="15.75" customHeight="1" s="31"/>
-    <row r="738" ht="15.75" customHeight="1" s="31"/>
-    <row r="739" ht="15.75" customHeight="1" s="31"/>
-    <row r="740" ht="15.75" customHeight="1" s="31"/>
-    <row r="741" ht="15.75" customHeight="1" s="31"/>
-    <row r="742" ht="15.75" customHeight="1" s="31"/>
-    <row r="743" ht="15.75" customHeight="1" s="31"/>
-    <row r="744" ht="15.75" customHeight="1" s="31"/>
-    <row r="745" ht="15.75" customHeight="1" s="31"/>
-    <row r="746" ht="15.75" customHeight="1" s="31"/>
-    <row r="747" ht="15.75" customHeight="1" s="31"/>
-    <row r="748" ht="15.75" customHeight="1" s="31"/>
-    <row r="749" ht="15.75" customHeight="1" s="31"/>
-    <row r="750" ht="15.75" customHeight="1" s="31"/>
-    <row r="751" ht="15.75" customHeight="1" s="31"/>
-    <row r="752" ht="15.75" customHeight="1" s="31"/>
-    <row r="753" ht="15.75" customHeight="1" s="31"/>
-    <row r="754" ht="15.75" customHeight="1" s="31"/>
-    <row r="755" ht="15.75" customHeight="1" s="31"/>
-    <row r="756" ht="15.75" customHeight="1" s="31"/>
-    <row r="757" ht="15.75" customHeight="1" s="31"/>
-    <row r="758" ht="15.75" customHeight="1" s="31"/>
-    <row r="759" ht="15.75" customHeight="1" s="31"/>
-    <row r="760" ht="15.75" customHeight="1" s="31"/>
-    <row r="761" ht="15.75" customHeight="1" s="31"/>
-    <row r="762" ht="15.75" customHeight="1" s="31"/>
-    <row r="763" ht="15.75" customHeight="1" s="31"/>
-    <row r="764" ht="15.75" customHeight="1" s="31"/>
-    <row r="765" ht="15.75" customHeight="1" s="31"/>
-    <row r="766" ht="15.75" customHeight="1" s="31"/>
-    <row r="767" ht="15.75" customHeight="1" s="31"/>
-    <row r="768" ht="15.75" customHeight="1" s="31"/>
-    <row r="769" ht="15.75" customHeight="1" s="31"/>
-    <row r="770" ht="15.75" customHeight="1" s="31"/>
-    <row r="771" ht="15.75" customHeight="1" s="31"/>
-    <row r="772" ht="15.75" customHeight="1" s="31"/>
-    <row r="773" ht="15.75" customHeight="1" s="31"/>
-    <row r="774" ht="15.75" customHeight="1" s="31"/>
-    <row r="775" ht="15.75" customHeight="1" s="31"/>
-    <row r="776" ht="15.75" customHeight="1" s="31"/>
-    <row r="777" ht="15.75" customHeight="1" s="31"/>
-    <row r="778" ht="15.75" customHeight="1" s="31"/>
-    <row r="779" ht="15.75" customHeight="1" s="31"/>
-    <row r="780" ht="15.75" customHeight="1" s="31"/>
-    <row r="781" ht="15.75" customHeight="1" s="31"/>
-    <row r="782" ht="15.75" customHeight="1" s="31"/>
-    <row r="783" ht="15.75" customHeight="1" s="31"/>
-    <row r="784" ht="15.75" customHeight="1" s="31"/>
-    <row r="785" ht="15.75" customHeight="1" s="31"/>
-    <row r="786" ht="15.75" customHeight="1" s="31"/>
-    <row r="787" ht="15.75" customHeight="1" s="31"/>
-    <row r="788" ht="15.75" customHeight="1" s="31"/>
-    <row r="789" ht="15.75" customHeight="1" s="31"/>
-    <row r="790" ht="15.75" customHeight="1" s="31"/>
-    <row r="791" ht="15.75" customHeight="1" s="31"/>
-    <row r="792" ht="15.75" customHeight="1" s="31"/>
-    <row r="793" ht="15.75" customHeight="1" s="31"/>
-    <row r="794" ht="15.75" customHeight="1" s="31"/>
-    <row r="795" ht="15.75" customHeight="1" s="31"/>
-    <row r="796" ht="15.75" customHeight="1" s="31"/>
-    <row r="797" ht="15.75" customHeight="1" s="31"/>
-    <row r="798" ht="15.75" customHeight="1" s="31"/>
-    <row r="799" ht="15.75" customHeight="1" s="31"/>
-    <row r="800" ht="15.75" customHeight="1" s="31"/>
-    <row r="801" ht="15.75" customHeight="1" s="31"/>
-    <row r="802" ht="15.75" customHeight="1" s="31"/>
-    <row r="803" ht="15.75" customHeight="1" s="31"/>
-    <row r="804" ht="15.75" customHeight="1" s="31"/>
-    <row r="805" ht="15.75" customHeight="1" s="31"/>
-    <row r="806" ht="15.75" customHeight="1" s="31"/>
-    <row r="807" ht="15.75" customHeight="1" s="31"/>
-    <row r="808" ht="15.75" customHeight="1" s="31"/>
-    <row r="809" ht="15.75" customHeight="1" s="31"/>
-    <row r="810" ht="15.75" customHeight="1" s="31"/>
-    <row r="811" ht="15.75" customHeight="1" s="31"/>
-    <row r="812" ht="15.75" customHeight="1" s="31"/>
-    <row r="813" ht="15.75" customHeight="1" s="31"/>
-    <row r="814" ht="15.75" customHeight="1" s="31"/>
-    <row r="815" ht="15.75" customHeight="1" s="31"/>
-    <row r="816" ht="15.75" customHeight="1" s="31"/>
-    <row r="817" ht="15.75" customHeight="1" s="31"/>
-    <row r="818" ht="15.75" customHeight="1" s="31"/>
-    <row r="819" ht="15.75" customHeight="1" s="31"/>
-    <row r="820" ht="15.75" customHeight="1" s="31"/>
-    <row r="821" ht="15.75" customHeight="1" s="31"/>
-    <row r="822" ht="15.75" customHeight="1" s="31"/>
-    <row r="823" ht="15.75" customHeight="1" s="31"/>
-    <row r="824" ht="15.75" customHeight="1" s="31"/>
-    <row r="825" ht="15.75" customHeight="1" s="31"/>
-    <row r="826" ht="15.75" customHeight="1" s="31"/>
-    <row r="827" ht="15.75" customHeight="1" s="31"/>
-    <row r="828" ht="15.75" customHeight="1" s="31"/>
-    <row r="829" ht="15.75" customHeight="1" s="31"/>
-    <row r="830" ht="15.75" customHeight="1" s="31"/>
-    <row r="831" ht="15.75" customHeight="1" s="31"/>
-    <row r="832" ht="15.75" customHeight="1" s="31"/>
-    <row r="833" ht="15.75" customHeight="1" s="31"/>
-    <row r="834" ht="15.75" customHeight="1" s="31"/>
-    <row r="835" ht="15.75" customHeight="1" s="31"/>
-    <row r="836" ht="15.75" customHeight="1" s="31"/>
-    <row r="837" ht="15.75" customHeight="1" s="31"/>
-    <row r="838" ht="15.75" customHeight="1" s="31"/>
-    <row r="839" ht="15.75" customHeight="1" s="31"/>
-    <row r="840" ht="15.75" customHeight="1" s="31"/>
-    <row r="841" ht="15.75" customHeight="1" s="31"/>
-    <row r="842" ht="15.75" customHeight="1" s="31"/>
-    <row r="843" ht="15.75" customHeight="1" s="31"/>
-    <row r="844" ht="15.75" customHeight="1" s="31"/>
-    <row r="845" ht="15.75" customHeight="1" s="31"/>
-    <row r="846" ht="15.75" customHeight="1" s="31"/>
-    <row r="847" ht="15.75" customHeight="1" s="31"/>
-    <row r="848" ht="15.75" customHeight="1" s="31"/>
-    <row r="849" ht="15.75" customHeight="1" s="31"/>
-    <row r="850" ht="15.75" customHeight="1" s="31"/>
-    <row r="851" ht="15.75" customHeight="1" s="31"/>
-    <row r="852" ht="15.75" customHeight="1" s="31"/>
-    <row r="853" ht="15.75" customHeight="1" s="31"/>
-    <row r="854" ht="15.75" customHeight="1" s="31"/>
-    <row r="855" ht="15.75" customHeight="1" s="31"/>
-    <row r="856" ht="15.75" customHeight="1" s="31"/>
-    <row r="857" ht="15.75" customHeight="1" s="31"/>
-    <row r="858" ht="15.75" customHeight="1" s="31"/>
-    <row r="859" ht="15.75" customHeight="1" s="31"/>
-    <row r="860" ht="15.75" customHeight="1" s="31"/>
-    <row r="861" ht="15.75" customHeight="1" s="31"/>
-    <row r="862" ht="15.75" customHeight="1" s="31"/>
-    <row r="863" ht="15.75" customHeight="1" s="31"/>
-    <row r="864" ht="15.75" customHeight="1" s="31"/>
-    <row r="865" ht="15.75" customHeight="1" s="31"/>
-    <row r="866" ht="15.75" customHeight="1" s="31"/>
-    <row r="867" ht="15.75" customHeight="1" s="31"/>
-    <row r="868" ht="15.75" customHeight="1" s="31"/>
-    <row r="869" ht="15.75" customHeight="1" s="31"/>
-    <row r="870" ht="15.75" customHeight="1" s="31"/>
-    <row r="871" ht="15.75" customHeight="1" s="31"/>
-    <row r="872" ht="15.75" customHeight="1" s="31"/>
-    <row r="873" ht="15.75" customHeight="1" s="31"/>
-    <row r="874" ht="15.75" customHeight="1" s="31"/>
-    <row r="875" ht="15.75" customHeight="1" s="31"/>
-    <row r="876" ht="15.75" customHeight="1" s="31"/>
-    <row r="877" ht="15.75" customHeight="1" s="31"/>
-    <row r="878" ht="15.75" customHeight="1" s="31"/>
-    <row r="879" ht="15.75" customHeight="1" s="31"/>
-    <row r="880" ht="15.75" customHeight="1" s="31"/>
-    <row r="881" ht="15.75" customHeight="1" s="31"/>
-    <row r="882" ht="15.75" customHeight="1" s="31"/>
-    <row r="883" ht="15.75" customHeight="1" s="31"/>
-    <row r="884" ht="15.75" customHeight="1" s="31"/>
-    <row r="885" ht="15.75" customHeight="1" s="31"/>
-    <row r="886" ht="15.75" customHeight="1" s="31"/>
-    <row r="887" ht="15.75" customHeight="1" s="31"/>
-    <row r="888" ht="15.75" customHeight="1" s="31"/>
-    <row r="889" ht="15.75" customHeight="1" s="31"/>
-    <row r="890" ht="15.75" customHeight="1" s="31"/>
-    <row r="891" ht="15.75" customHeight="1" s="31"/>
-    <row r="892" ht="15.75" customHeight="1" s="31"/>
-    <row r="893" ht="15.75" customHeight="1" s="31"/>
-    <row r="894" ht="15.75" customHeight="1" s="31"/>
-    <row r="895" ht="15.75" customHeight="1" s="31"/>
-    <row r="896" ht="15.75" customHeight="1" s="31"/>
-    <row r="897" ht="15.75" customHeight="1" s="31"/>
-    <row r="898" ht="15.75" customHeight="1" s="31"/>
-    <row r="899" ht="15.75" customHeight="1" s="31"/>
-    <row r="900" ht="15.75" customHeight="1" s="31"/>
-    <row r="901" ht="15.75" customHeight="1" s="31"/>
-    <row r="902" ht="15.75" customHeight="1" s="31"/>
-    <row r="903" ht="15.75" customHeight="1" s="31"/>
-    <row r="904" ht="15.75" customHeight="1" s="31"/>
-    <row r="905" ht="15.75" customHeight="1" s="31"/>
-    <row r="906" ht="15.75" customHeight="1" s="31"/>
-    <row r="907" ht="15.75" customHeight="1" s="31"/>
-    <row r="908" ht="15.75" customHeight="1" s="31"/>
-    <row r="909" ht="15.75" customHeight="1" s="31"/>
-    <row r="910" ht="15.75" customHeight="1" s="31"/>
-    <row r="911" ht="15.75" customHeight="1" s="31"/>
-    <row r="912" ht="15.75" customHeight="1" s="31"/>
-    <row r="913" ht="15.75" customHeight="1" s="31"/>
-    <row r="914" ht="15.75" customHeight="1" s="31"/>
-    <row r="915" ht="15.75" customHeight="1" s="31"/>
-    <row r="916" ht="15.75" customHeight="1" s="31"/>
-    <row r="917" ht="15.75" customHeight="1" s="31"/>
-    <row r="918" ht="15.75" customHeight="1" s="31"/>
-    <row r="919" ht="15.75" customHeight="1" s="31"/>
-    <row r="920" ht="15.75" customHeight="1" s="31"/>
-    <row r="921" ht="15.75" customHeight="1" s="31"/>
-    <row r="922" ht="15.75" customHeight="1" s="31"/>
-    <row r="923" ht="15.75" customHeight="1" s="31"/>
-    <row r="924" ht="15.75" customHeight="1" s="31"/>
-    <row r="925" ht="15.75" customHeight="1" s="31"/>
-    <row r="926" ht="15.75" customHeight="1" s="31"/>
-    <row r="927" ht="15.75" customHeight="1" s="31"/>
-    <row r="928" ht="15.75" customHeight="1" s="31"/>
-    <row r="929" ht="15.75" customHeight="1" s="31"/>
-    <row r="930" ht="15.75" customHeight="1" s="31"/>
-    <row r="931" ht="15.75" customHeight="1" s="31"/>
-    <row r="932" ht="15.75" customHeight="1" s="31"/>
-    <row r="933" ht="15.75" customHeight="1" s="31"/>
-    <row r="934" ht="15.75" customHeight="1" s="31"/>
-    <row r="935" ht="15.75" customHeight="1" s="31"/>
-    <row r="936" ht="15.75" customHeight="1" s="31"/>
-    <row r="937" ht="15.75" customHeight="1" s="31"/>
-    <row r="938" ht="15.75" customHeight="1" s="31"/>
-    <row r="939" ht="15.75" customHeight="1" s="31"/>
-    <row r="940" ht="15.75" customHeight="1" s="31"/>
-    <row r="941" ht="15.75" customHeight="1" s="31"/>
-    <row r="942" ht="15.75" customHeight="1" s="31"/>
-    <row r="943" ht="15.75" customHeight="1" s="31"/>
-    <row r="944" ht="15.75" customHeight="1" s="31"/>
-    <row r="945" ht="15.75" customHeight="1" s="31"/>
-    <row r="946" ht="15.75" customHeight="1" s="31"/>
-    <row r="947" ht="15.75" customHeight="1" s="31"/>
-    <row r="948" ht="15.75" customHeight="1" s="31"/>
-    <row r="949" ht="15.75" customHeight="1" s="31"/>
-    <row r="950" ht="15.75" customHeight="1" s="31"/>
-    <row r="951" ht="15.75" customHeight="1" s="31"/>
-    <row r="952" ht="15.75" customHeight="1" s="31"/>
-    <row r="953" ht="15.75" customHeight="1" s="31"/>
-    <row r="954" ht="15.75" customHeight="1" s="31"/>
-    <row r="955" ht="15.75" customHeight="1" s="31"/>
-    <row r="956" ht="15.75" customHeight="1" s="31"/>
-    <row r="957" ht="15.75" customHeight="1" s="31"/>
-    <row r="958" ht="15.75" customHeight="1" s="31"/>
-    <row r="959" ht="15.75" customHeight="1" s="31"/>
-    <row r="960" ht="15.75" customHeight="1" s="31"/>
-    <row r="961" ht="15.75" customHeight="1" s="31"/>
-    <row r="962" ht="15.75" customHeight="1" s="31"/>
-    <row r="963" ht="15.75" customHeight="1" s="31"/>
-    <row r="964" ht="15.75" customHeight="1" s="31"/>
-    <row r="965" ht="15.75" customHeight="1" s="31"/>
-    <row r="966" ht="15.75" customHeight="1" s="31"/>
-    <row r="967" ht="15.75" customHeight="1" s="31"/>
-    <row r="968" ht="15.75" customHeight="1" s="31"/>
-    <row r="969" ht="15.75" customHeight="1" s="31"/>
-    <row r="970" ht="15.75" customHeight="1" s="31"/>
-    <row r="971" ht="15.75" customHeight="1" s="31"/>
-    <row r="972" ht="15.75" customHeight="1" s="31"/>
-    <row r="973" ht="15.75" customHeight="1" s="31"/>
-    <row r="974" ht="15.75" customHeight="1" s="31"/>
-    <row r="975" ht="15.75" customHeight="1" s="31"/>
-    <row r="976" ht="15.75" customHeight="1" s="31"/>
-    <row r="977" ht="15.75" customHeight="1" s="31"/>
-    <row r="978" ht="15.75" customHeight="1" s="31"/>
-    <row r="979" ht="15.75" customHeight="1" s="31"/>
-    <row r="980" ht="15.75" customHeight="1" s="31"/>
-    <row r="981" ht="15.75" customHeight="1" s="31"/>
-    <row r="982" ht="15.75" customHeight="1" s="31"/>
-    <row r="983" ht="15.75" customHeight="1" s="31"/>
-    <row r="984" ht="15.75" customHeight="1" s="31"/>
-    <row r="985" ht="15.75" customHeight="1" s="31"/>
-    <row r="986" ht="15.75" customHeight="1" s="31"/>
-    <row r="987" ht="15.75" customHeight="1" s="31"/>
-    <row r="988" ht="15.75" customHeight="1" s="31"/>
-    <row r="989" ht="15.75" customHeight="1" s="31"/>
-    <row r="990" ht="15.75" customHeight="1" s="31"/>
-    <row r="991" ht="15.75" customHeight="1" s="31"/>
-    <row r="992" ht="15.75" customHeight="1" s="31"/>
-    <row r="993" ht="15.75" customHeight="1" s="31"/>
-    <row r="994" ht="15.75" customHeight="1" s="31"/>
-    <row r="995" ht="15.75" customHeight="1" s="31"/>
-    <row r="996" ht="15.75" customHeight="1" s="31"/>
-    <row r="997" ht="15.75" customHeight="1" s="31"/>
-    <row r="998" ht="15.75" customHeight="1" s="31"/>
-    <row r="999" ht="15.75" customHeight="1" s="31"/>
-    <row r="1000" ht="15.75" customHeight="1" s="31"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col width="24.75" customWidth="1" style="31" min="1" max="1"/>
-    <col width="56.75" customWidth="1" style="31" min="2" max="2"/>
-    <col width="12.63" customWidth="1" style="31" min="3" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="31">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="31">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC02</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30.75" customHeight="1" s="31">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page, all fields blank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30.75" customHeight="1" s="31">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Leave "Event name" empty
-2. Click "Save draft"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" s="31">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event name: "" (empty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="31">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The page does not move on. A message "Give the event a name so you can find it again." appears under Event name, and the cursor moves there.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.25" customHeight="1" s="31">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="31">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="26" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" s="31"/>
-    <row r="10" ht="15.75" customHeight="1" s="31">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="31">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The page does not move on. A message "Give the event a name so you can find it again." appears under Event name, and the cursor moves there.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="31">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="31">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" s="31">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" s="31">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="n">
-        <v>46281</v>
-      </c>
-      <c r="E15" s="24" t="n"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="31"/>
-    <row r="17" ht="15.75" customHeight="1" s="31"/>
-    <row r="18" ht="15.75" customHeight="1" s="31">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="31">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>The page does not navigate away. An error message: "Give the event a name so you can find it again." appears under the Event name field. The page scrolls to bring the field into view, and focus moves to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="31">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="31">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="31">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="31">
-      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Date of Execution</t>
         </is>
@@ -16121,7 +16174,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="31" min="1" max="1"/>
@@ -16143,9 +16196,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC03</t>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC02</t>
         </is>
       </c>
     </row>
@@ -16155,9 +16208,9 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page.</t>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page, all fields blank.</t>
         </is>
       </c>
     </row>
@@ -16167,9 +16220,9 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Enter "   " (three spaces) into Event name
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. Leave "Event name" empty
 2. Click "Save draft"</t>
         </is>
       </c>
@@ -16180,9 +16233,9 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event name: "   " (3 spaces)</t>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Event name: "" (empty)</t>
         </is>
       </c>
     </row>
@@ -16192,9 +16245,9 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The page does not move on. The same message, "Give the event a name so you can find it again.", appears under Event name — typing only spaces counts as leaving it blank.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The page does not move on. A message "Give the event a name so you can find it again." appears under Event name, and the cursor moves there.</t>
         </is>
       </c>
     </row>
@@ -16204,7 +16257,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -16236,9 +16289,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The page does not move on. The same message, "Give the event a name so you can find it again.", appears under Event name — typing only spaces counts as leaving it blank.</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The page does not move on. A message "Give the event a name so you can find it again." appears under Event name, and the cursor moves there.</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16325,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -16287,6 +16340,7 @@
       <c r="B15" s="26" t="n">
         <v>46281</v>
       </c>
+      <c r="E15" s="24" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="31"/>
     <row r="17" ht="15.75" customHeight="1" s="31"/>
@@ -16304,7 +16358,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>The page does not navigate away. An error message: "Give the event a name so you can find it again." appears under the Event name field. The page scrolls to bring the field into view, and focus moves to it.</t>
         </is>
@@ -17345,7 +17399,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="31" min="1" max="1"/>
@@ -17367,21 +17421,21 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.25" customHeight="1" s="31">
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30.75" customHeight="1" s="31">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Seeded account rachel.ng@meridianfina.com owns the seeded draft "Q1 Investor Update (rough idea)" and the seeded, already-completed event "Meridian Compliance Training".</t>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page.</t>
         </is>
       </c>
     </row>
@@ -17391,10 +17445,10 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Log in as rachel.ng@meridianfina.com / password123
-2. Open the "My events" page</t>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. Enter "   " (three spaces) into Event name
+2. Click "Save draft"</t>
         </is>
       </c>
     </row>
@@ -17404,21 +17458,21 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>N/A — uses seeded data</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="31">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Event name: "   " (3 spaces)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="31">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The page shows a "Drafts — not yet submitted (1)" section listing "Q1 Investor Update (rough idea)" with a grey "Draft" badge, sitting above and separate from the "Submitted" section, which lists "Meridian Compliance Training".</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The page does not move on. The same message, "Give the event a name so you can find it again.", appears under Event name — typing only spaces counts as leaving it blank.</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17482,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -17460,9 +17514,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The page shows a "Drafts — not yet submitted (1)" section listing "Q1 Investor Update (rough idea)" with a grey "Draft" badge, sitting above and separate from the "Submitted" section, which lists "Meridian Compliance Training".</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The page does not move on. The same message, "Give the event a name so you can find it again.", appears under Event name — typing only spaces counts as leaving it blank.</t>
         </is>
       </c>
     </row>
@@ -17496,7 +17550,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -17528,9 +17582,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>The page shows a "Drafts — not yet submitted (2)" section listing "Annual Partner Appreciation Dinner" and "Q1 Investor Update (rough idea)", both with a grey "Draft" badge, sitting above and separate from the "Submitted" section, which lists "Meridian Compliance Training".</t>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>The page does not navigate away. An error message: "Give the event a name so you can find it again." appears under the Event name field. The page scrolls to bring the field into view, and focus moves to it.</t>
         </is>
       </c>
     </row>
@@ -17542,7 +17596,7 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17552,9 +17606,9 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>Mismatch is due to a pre-condition gap in the test case, not an app defect as TC01 creates a persistent draft on this same seeded account and it isn't cleaned up, so the drafts count is order-dependent. Recommend isolating this test to a dedicated account or resetting drafts before running.</t>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -17582,72 +17636,12 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" s="31"/>
     <row r="25" ht="15.75" customHeight="1" s="31"/>
-    <row r="26" ht="15.75" customHeight="1" s="31">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" s="31">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>The page shows a "Drafts — not yet submitted (1)" section listing "Q1 Investor Update (rough idea)" with a grey "Draft" badge, sitting above and separate from the "Submitted" section, which lists "Meridian Compliance Training".</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" s="31">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" s="31">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Feedbacked to Kristen and she made the update</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" s="31">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" s="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="n">
-        <v>46282</v>
-      </c>
-    </row>
+    <row r="26" ht="15.75" customHeight="1" s="31"/>
+    <row r="27" ht="15.75" customHeight="1" s="31"/>
+    <row r="28" ht="15.75" customHeight="1" s="31"/>
+    <row r="29" ht="15.75" customHeight="1" s="31"/>
+    <row r="30" ht="15.75" customHeight="1" s="31"/>
+    <row r="31" ht="15.75" customHeight="1" s="31"/>
     <row r="32" ht="15.75" customHeight="1" s="31"/>
     <row r="33" ht="15.75" customHeight="1" s="31"/>
     <row r="34" ht="15.75" customHeight="1" s="31"/>
@@ -18629,7 +18623,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="31" min="1" max="1"/>
@@ -18651,35 +18645,34 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC05</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30.75" customHeight="1" s="31">
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.25" customHeight="1" s="31">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Seeded draft "Q1 Investor Update (rough idea)" owned by rachel.ng@meridianfina.com.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1" s="31">
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Seeded account rachel.ng@meridianfina.com owns the seeded draft "Q1 Investor Update (rough idea)" and the seeded, already-completed event "Meridian Compliance Training".</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30.75" customHeight="1" s="31">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>1. Log in as rachel.ng@meridianfina.com / password123
-2. Open the "My events" page
-3. Click the "Q1 Investor Update (rough idea)" row</t>
+2. Open the "My events" page</t>
         </is>
       </c>
     </row>
@@ -18689,21 +18682,21 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>N/A — uses seeded data</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="44.25" customHeight="1" s="31">
+    <row r="6" ht="57.75" customHeight="1" s="31">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The "Edit draft" page opens, showing the subtitle "Pick up where you left off. Nothing here is sent until you submit it." together with a "Draft" badge next to the title.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The page shows a "Drafts — not yet submitted (1)" section listing "Q1 Investor Update (rough idea)" with a grey "Draft" badge, sitting above and separate from the "Submitted" section, which lists "Meridian Compliance Training".</t>
         </is>
       </c>
     </row>
@@ -18713,7 +18706,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -18745,9 +18738,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The "Edit draft" page opens, showing the subtitle "Pick up where you left off. Nothing here is sent until you submit it." together with a "Draft" badge next to the title.</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The page shows a "Drafts — not yet submitted (1)" section listing "Q1 Investor Update (rough idea)" with a grey "Draft" badge, sitting above and separate from the "Submitted" section, which lists "Meridian Compliance Training".</t>
         </is>
       </c>
     </row>
@@ -18781,7 +18774,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -18813,9 +18806,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>The "Edit draft" page opens, showing the subtitle "Pick up where you left off. Nothing here is sent until you submit it." together with a "Draft" badge next to the title.</t>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>The page shows a "Drafts — not yet submitted (2)" section listing "Annual Partner Appreciation Dinner" and "Q1 Investor Update (rough idea)", both with a grey "Draft" badge, sitting above and separate from the "Submitted" section, which lists "Meridian Compliance Training".</t>
         </is>
       </c>
     </row>
@@ -18827,7 +18820,7 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -18837,9 +18830,9 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>Mismatch is due to a pre-condition gap in the test case, not an app defect as TC01 creates a persistent draft on this same seeded account and it isn't cleaned up, so the drafts count is order-dependent. Recommend isolating this test to a dedicated account or resetting drafts before running.</t>
         </is>
       </c>
     </row>
@@ -18867,12 +18860,72 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" s="31"/>
     <row r="25" ht="15.75" customHeight="1" s="31"/>
-    <row r="26" ht="15.75" customHeight="1" s="31"/>
-    <row r="27" ht="15.75" customHeight="1" s="31"/>
-    <row r="28" ht="15.75" customHeight="1" s="31"/>
-    <row r="29" ht="15.75" customHeight="1" s="31"/>
-    <row r="30" ht="15.75" customHeight="1" s="31"/>
-    <row r="31" ht="15.75" customHeight="1" s="31"/>
+    <row r="26" ht="15.75" customHeight="1" s="31">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="31">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>The page shows a "Drafts — not yet submitted (1)" section listing "Q1 Investor Update (rough idea)" with a grey "Draft" badge, sitting above and separate from the "Submitted" section, which lists "Meridian Compliance Training".</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="31">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="31">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Feedbacked to Kristen and she made the update</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="31">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>46282</v>
+      </c>
+    </row>
     <row r="32" ht="15.75" customHeight="1" s="31"/>
     <row r="33" ht="15.75" customHeight="1" s="31"/>
     <row r="34" ht="15.75" customHeight="1" s="31"/>
@@ -19876,37 +19929,35 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.25" customHeight="1" s="31">
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30.75" customHeight="1" s="31">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Seeded draft "Q1 Investor Update (rough idea)" owned by rachel.ng@meridianfina.com. Its saved description reads "Still checking dates with the exec team."</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.25" customHeight="1" s="31">
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Seeded draft "Q1 Investor Update (rough idea)" owned by rachel.ng@meridianfina.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="31">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>1. Log in as rachel.ng@meridianfina.com / password123
-2. Log out
-3. Log back in as rachel.ng@meridianfina.com / password123
-4. Open the "My events" page
-5. Click the "Q1 Investor Update (rough idea)" row</t>
+2. Open the "My events" page
+3. Click the "Q1 Investor Update (rough idea)" row</t>
         </is>
       </c>
     </row>
@@ -19916,22 +19967,21 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Login: rachel.ng@meridianfina.com / password123</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="31">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>N/A — uses seeded data</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="31">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The "Edit draft" page opens with every previously saved value already filled in, including the Description field reading "Still checking dates with the exec team."
-The Draft badge is still shown.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The "Edit draft" page opens, showing the subtitle "Pick up where you left off. Nothing here is sent until you submit it." together with a "Draft" badge next to the title.</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19991,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -19973,10 +20023,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The "Edit draft" page opens with every previously saved value already filled in, including the Description field reading "Still checking dates with the exec team."
-The Draft badge is still shown.</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The "Edit draft" page opens, showing the subtitle "Pick up where you left off. Nothing here is sent until you submit it." together with a "Draft" badge next to the title.</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20059,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -20042,10 +20091,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>The "Edit draft" page opens with every previously saved value already filled in, including the event name reading" Q1 Investor Update (rough idea)" and the Description field reading "Still checking dates with the exec team."
-The Draft badge is still shown.</t>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>The "Edit draft" page opens, showing the subtitle "Pick up where you left off. Nothing here is sent until you submit it." together with a "Draft" badge next to the title.</t>
         </is>
       </c>
     </row>
@@ -21106,34 +21154,37 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC07</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="84.75" customHeight="1" s="31">
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.25" customHeight="1" s="31">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Seeded draft "Q1 Investor Update (rough idea)" is owned by rachel.ng@meridianfina.com (Meridian Financial Group). budi.santoso@nusantaratec.com is an Organiser at an unrelated organisation, Nusantara Tech Labs. Rachel's draft's edit-page web address has been copied (e.g. from the address bar while logged in as her).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1" s="31">
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Seeded draft "Q1 Investor Update (rough idea)" owned by rachel.ng@meridianfina.com. Its saved description reads "Still checking dates with the exec team."</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.25" customHeight="1" s="31">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Log in as budi.santoso@nusantaratec.com / password123
-2. Paste Rachel's draft's edit-page address into the browser and go to it</t>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. Log in as rachel.ng@meridianfina.com / password123
+2. Log out
+3. Log back in as rachel.ng@meridianfina.com / password123
+4. Open the "My events" page
+5. Click the "Q1 Investor Update (rough idea)" row</t>
         </is>
       </c>
     </row>
@@ -21143,21 +21194,22 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Requester: budi.santoso@nusantaratec.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="31">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Login: rachel.ng@meridianfina.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="31">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The page shows "This draft could not be found. It may have been removed, or it isn't yours." instead of the form — Budi never sees any of Rachel's draft content.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The "Edit draft" page opens with every previously saved value already filled in, including the Description field reading "Still checking dates with the exec team."
+The Draft badge is still shown.</t>
         </is>
       </c>
     </row>
@@ -21167,7 +21219,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -21199,9 +21251,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The page shows "This draft could not be found. It may have been removed, or it isn't yours." instead of the form — Budi never sees any of Rachel's draft content.</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The "Edit draft" page opens with every previously saved value already filled in, including the Description field reading "Still checking dates with the exec team."
+The Draft badge is still shown.</t>
         </is>
       </c>
     </row>
@@ -21235,7 +21288,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -21267,9 +21320,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>The page shows an inline error banner "This draft could not be found. It may have been removed, or it isn't yours." instead of the form, Budi is unable to see any of Rachel's draft content.</t>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>The "Edit draft" page opens with every previously saved value already filled in, including the event name reading" Q1 Investor Update (rough idea)" and the Description field reading "Still checking dates with the exec team."
+The Draft badge is still shown.</t>
         </is>
       </c>
     </row>
@@ -22330,21 +22384,21 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-24-TC08</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30.75" customHeight="1" s="31">
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>SPM-24-TC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="84.75" customHeight="1" s="31">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Seeded draft "Q1 Investor Update (rough idea)" exists. No one is logged in.</t>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Seeded draft "Q1 Investor Update (rough idea)" is owned by rachel.ng@meridianfina.com (Meridian Financial Group). budi.santoso@nusantaratec.com is an Organiser at an unrelated organisation, Nusantara Tech Labs. Rachel's draft's edit-page web address has been copied (e.g. from the address bar while logged in as her).</t>
         </is>
       </c>
     </row>
@@ -22354,10 +22408,10 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Make sure you are logged out
-2. Paste the draft's edit-page address into the browser and go to it</t>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>1. Log in as budi.santoso@nusantaratec.com / password123
+2. Paste Rachel's draft's edit-page address into the browser and go to it</t>
         </is>
       </c>
     </row>
@@ -22367,9 +22421,9 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Requester: budi.santoso@nusantaratec.com</t>
         </is>
       </c>
     </row>
@@ -22379,9 +22433,9 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The browser is redirected to the login page instead of showing the draft. After logging in, it takes you straight back to the draft's edit page.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>The page shows "This draft could not be found. It may have been removed, or it isn't yours." instead of the form — Budi never sees any of Rachel's draft content.</t>
         </is>
       </c>
     </row>
@@ -22391,7 +22445,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -22423,9 +22477,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>The browser is redirected to the login page instead of showing the draft. After logging in, it takes you straight back to the draft's edit page.</t>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>The page shows "This draft could not be found. It may have been removed, or it isn't yours." instead of the form — Budi never sees any of Rachel's draft content.</t>
         </is>
       </c>
     </row>
@@ -22459,7 +22513,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -22491,9 +22545,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Pasting the draft's edit URL while logged out redirects to the login page displays the message "Your session expired. Log in to continue where you left off." After logging in successfully, the browser is redirected back to the draft's edit page</t>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>The page shows an inline error banner "This draft could not be found. It may have been removed, or it isn't yours." instead of the form, Budi is unable to see any of Rachel's draft content.</t>
         </is>
       </c>
     </row>
